--- a/celine/aventura/GC_BID_FORM_AVENTURA_LUX_BRAND_COMPANY.xlsx
+++ b/celine/aventura/GC_BID_FORM_AVENTURA_LUX_BRAND_COMPANY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\0B2Ik8SwJAxx-UUUzSTJLWmlNd0U\Lux\CLIENTS\Celine\26_Aventura Mall - Celine\20251216_GC BID PACKAGE\BID FORM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBF86A7-3C73-4137-885A-E3F741A52E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95A15E2-D027-4976-ADF7-DFA81D959BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BID FORM " sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="219">
   <si>
     <t>PROJECT:</t>
   </si>
@@ -97,7 +97,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">All items listed are for GC to </t>
     </r>
@@ -107,7 +106,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>FURNISH &amp; INSTALL</t>
     </r>
@@ -116,7 +114,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> unless noted otherwise</t>
     </r>
@@ -144,21 +141,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily Site Cleaning </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Site Cleans  (3 MIN PROFESSIONAL  REQUIRED) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building Permit and Fees </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temporary Utilities </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Documents and Controls </t>
   </si>
   <si>
     <r>
@@ -166,7 +148,49 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Barricade installation and Removal + Coordination of installation of Barricade Graphic  (include making good LL finishes including LL tiles, transitions and finishes) - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>Touch up finishes after barricade is removed and Barricade rental.  Barricade graphics are to be supplied by Celine</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily Site Cleaning </t>
+  </si>
+  <si>
+    <t>LBC holds each sub to daily cleaning before they leave so this is covered in the bid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Site Cleans  (3 MIN PROFESSIONAL  REQUIRED) </t>
+  </si>
+  <si>
+    <t>Stripping and waxing of BOH VCT areas now included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building Permit and Fees </t>
+  </si>
+  <si>
+    <t>Allowance - Additionl permit fees above allowance will be a pass through expense at no markup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temporary Utilities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Documents and Controls </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">(9) Dumpsters and Waste Removal (including millwork debris and crates) - </t>
     </r>
@@ -176,7 +200,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>No dumpsters provide for store stocking</t>
     </r>
@@ -185,7 +208,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 to comply with Building Rules and Regulations </t>
@@ -213,12 +235,18 @@
     <t xml:space="preserve">Samples as required </t>
   </si>
   <si>
+    <t>Samples including level 5 drywall finish are included</t>
+  </si>
+  <si>
     <t>02 _ Site Construction</t>
   </si>
   <si>
     <t xml:space="preserve">Demolition ( include and specify night if required) </t>
   </si>
   <si>
+    <t>Field review of landlord demolition requirerd to verify space at handover to GC.  Added cost for demo per revision 6/Permit revision #1 4/9/26</t>
+  </si>
+  <si>
     <t>03 _ Concrete</t>
   </si>
   <si>
@@ -252,9 +280,24 @@
     <t xml:space="preserve">Stone Storage by GC. Stone delivery to  site by GC </t>
   </si>
   <si>
+    <t>Revised per request from Celine - Storage and Receiving</t>
+  </si>
+  <si>
     <t xml:space="preserve">Drylay required for 20 tiles Maximum </t>
   </si>
   <si>
+    <t xml:space="preserve">FLOOR: Basaltite- 1197mmx11587mm Basaltina Marble Floor Tiles;  </t>
+  </si>
+  <si>
+    <t>Install for Landlord attic stock tile listed below</t>
+  </si>
+  <si>
+    <t>Land Lord attic stock tile or stone - Assumes 162 SQFT and $34.00/SQFT for Material</t>
+  </si>
+  <si>
+    <t>Supply of Landlord attic stock tile - 4 courses of tile</t>
+  </si>
+  <si>
     <t>05_ Metals</t>
   </si>
   <si>
@@ -291,6 +334,9 @@
     <t>Rough Carpentry , Blocking , and Back Framing</t>
   </si>
   <si>
+    <t>Included in framing number below and breakout numbers below</t>
+  </si>
+  <si>
     <t xml:space="preserve">Plywood sheathing for Millwork installation </t>
   </si>
   <si>
@@ -336,6 +382,9 @@
     <t>Storefront system (Includes Glazing, Mullions, and Install)</t>
   </si>
   <si>
+    <t xml:space="preserve"> Entry doors included in pricing</t>
+  </si>
+  <si>
     <t xml:space="preserve">Storefront Glazing </t>
   </si>
   <si>
@@ -358,188 +407,6 @@
   </si>
   <si>
     <t xml:space="preserve">Internal Doors supply and Install </t>
-  </si>
-  <si>
-    <t>09_ Finishes</t>
-  </si>
-  <si>
-    <t>Drywall (wall type finishes) - Walls and Ceilings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceiling Drywall </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACT Ceiling </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vinyl flooring </t>
-  </si>
-  <si>
-    <t>Vinyl Base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Painting (Level 5 Finish on Sales Floor - walls, ceiling &amp; ceiling coves) - Includes BOH walls and ceilings
-</t>
-  </si>
-  <si>
-    <t>Misc.: [M-1] Polished Stainless Steel Base - Install in areas not on sales floor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT-1 Wall Finish
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stone flooring </t>
-  </si>
-  <si>
-    <t>10_ Specialties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign Permits including UL listing fees </t>
-  </si>
-  <si>
-    <t>Logo installation (Sign Install - Sign supply by MWC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lockers: Coordination of Owner Vendor Installation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storage Shelving:  Coordination of Owner Vendor Installation </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire extinguishers and cabinets </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supply and install of Braille and Tactile signage </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bathroom Accessories </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Restroom  Toilet Paper Holder</t>
-  </si>
-  <si>
-    <t>Restroom Flush Actuator Plate</t>
-  </si>
-  <si>
-    <t>Restroom Straight Grab Bar</t>
-  </si>
-  <si>
-    <t>Restroom Coat Hook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restroom Mirrors </t>
-  </si>
-  <si>
-    <t>11_ Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitchen appliances supply and installation </t>
-  </si>
-  <si>
-    <t>Refrigerator</t>
-  </si>
-  <si>
-    <t>Dishwasher</t>
-  </si>
-  <si>
-    <t>Microwave</t>
-  </si>
-  <si>
-    <t>Water Machine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safe _  Coordination and Installation of Owner Supplied </t>
-  </si>
-  <si>
-    <t>12_ Furnishing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT USED </t>
-  </si>
-  <si>
-    <t>14_ Conveying Systems</t>
-  </si>
-  <si>
-    <t>15_ Fire Suppression</t>
-  </si>
-  <si>
-    <t>Sprinkler systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprinkler permits and Fees </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprinkler Testing and Commissioning </t>
-  </si>
-  <si>
-    <t>Sprinkler shut down (4 shutdowns included)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shop drawings and Coordination up to 3 revisions </t>
-  </si>
-  <si>
-    <t>Color match heads</t>
-  </si>
-  <si>
-    <t>16 _  Plumbing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plumbing Fixtures and Equipment : Supply And Install </t>
-  </si>
-  <si>
-    <t>Pantry Sink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Sink + Faucet  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drinking Fountain </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floor Drains </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water Meter </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plumbing permit and Fees </t>
-  </si>
-  <si>
-    <t>Other - Camera locate for plumbing tie-ins</t>
-  </si>
-  <si>
-    <t>17 _  Heating Ventilating and Air- Conditioning</t>
-  </si>
-  <si>
-    <t>HVAC Equipment  ( including F&amp;I of dampers, sensors, control systems, heaters, exhaust fans etc. ) ALL COST TO BE INCLUDED, GC TO PROVIDE SPECIAL PRICING ON ITEMS IF REQUIRED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diffusers and Grills - specify lead time </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVAC Ductwork and Distribution </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HVAC Permit and Fees </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing and Comissions </t>
-  </si>
-  <si>
-    <t>CONTROLS?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air Balance report </t>
-  </si>
-  <si>
-    <t>18 _ Electric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical distributions </t>
-  </si>
-  <si>
-    <t>Electrical Cabling and Conduits</t>
   </si>
   <si>
     <r>
@@ -547,7 +414,222 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Internal Doors Hardware and  Lockset Supply and Install </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(Door #08 and Door to unusable space)</t>
+    </r>
+  </si>
+  <si>
+    <t>5 point electrified lock included in pricing</t>
+  </si>
+  <si>
+    <t>09_ Finishes</t>
+  </si>
+  <si>
+    <t>Drywall (wall type finishes) - Walls and Ceilings</t>
+  </si>
+  <si>
+    <t>Level 5 finish mock up requested by Celine - Included in price and confrimed by subcontractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceiling Drywall </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACT Ceiling </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vinyl flooring </t>
+  </si>
+  <si>
+    <t>Vinyl Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Painting (Level 5 Finish on Sales Floor - walls, ceiling &amp; ceiling coves) - Includes BOH walls and ceilings
+</t>
+  </si>
+  <si>
+    <t>Misc.: [M-1] Polished Stainless Steel Base - Install in areas not on sales floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT-1 Wall Finish
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stone flooring </t>
+  </si>
+  <si>
+    <t>10_ Specialties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign Permits including UL listing fees </t>
+  </si>
+  <si>
+    <t>Logo installation (Sign Install - Sign supply by MWC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lockers: Coordination of Owner Vendor Installation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage Shelving:  Coordination of Owner Vendor Installation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire extinguishers and cabinets </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supply and install of Braille and Tactile signage </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bathroom Accessories </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Restroom  Toilet Paper Holder</t>
+  </si>
+  <si>
+    <t>Restroom Flush Actuator Plate</t>
+  </si>
+  <si>
+    <t>Restroom Straight Grab Bar</t>
+  </si>
+  <si>
+    <t>Restroom Coat Hook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restroom Mirrors </t>
+  </si>
+  <si>
+    <t>11_ Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitchen appliances supply and installation </t>
+  </si>
+  <si>
+    <t>Refrigerator</t>
+  </si>
+  <si>
+    <t>Dishwasher</t>
+  </si>
+  <si>
+    <t>Microwave</t>
+  </si>
+  <si>
+    <t>Water Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safe _  Coordination and Installation of Owner Supplied </t>
+  </si>
+  <si>
+    <t>12_ Furnishing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT USED </t>
+  </si>
+  <si>
+    <t>14_ Conveying Systems</t>
+  </si>
+  <si>
+    <t>15_ Fire Suppression</t>
+  </si>
+  <si>
+    <t>Sprinkler systems</t>
+  </si>
+  <si>
+    <t>Includes 3 additional sprinkler heads with 5' long branch pipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprinkler permits and Fees </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprinkler Testing and Commissioning </t>
+  </si>
+  <si>
+    <t>Sprinkler shut down (4 shutdowns included)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop drawings and Coordination up to 3 revisions </t>
+  </si>
+  <si>
+    <t>Color match heads</t>
+  </si>
+  <si>
+    <t>16 _  Plumbing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plumbing Fixtures and Equipment : Supply And Install </t>
+  </si>
+  <si>
+    <t>Pantry Sink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Sink + Faucet  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drinking Fountain </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor Drains </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water Meter </t>
+  </si>
+  <si>
+    <t>Included in plumbing number above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plumbing permit and Fees </t>
+  </si>
+  <si>
+    <t>Other - Camera locate for plumbing tie-ins</t>
+  </si>
+  <si>
+    <t>17 _  Heating Ventilating and Air- Conditioning</t>
+  </si>
+  <si>
+    <t>HVAC Equipment  ( including F&amp;I of dampers, sensors, control systems, heaters, exhaust fans etc. ) ALL COST TO BE INCLUDED, GC TO PROVIDE SPECIAL PRICING ON ITEMS IF REQUIRED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diffusers and Grills - specify lead time </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVAC Ductwork and Distribution </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HVAC Permit and Fees </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing and Comissions </t>
+  </si>
+  <si>
+    <t>CONTROLS?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air Balance report </t>
+  </si>
+  <si>
+    <t>18 _ Electric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrical distributions </t>
+  </si>
+  <si>
+    <t>ADT Rack, IT Rack, and Patch Panels by Owners Vendor</t>
+  </si>
+  <si>
+    <t>Electrical Cabling and Conduits</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Light switches, rectacaples,power and data outlets and finish plates </t>
     </r>
@@ -557,7 +639,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Included in above number)</t>
     </r>
@@ -571,7 +652,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Lighting at FOH  (Install Owner Supplied) </t>
     </r>
@@ -581,7 +661,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Included in above number)</t>
     </r>
@@ -592,7 +671,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Lighting at BOH (Furnish and Install by GC) </t>
     </r>
@@ -602,7 +680,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Included in above number)</t>
     </r>
@@ -613,7 +690,25 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ELECTRICAL Lighting drivers; Furnish and Install ALL in scope of work </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(114 drivers includes 5 spares)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">ELECTRICAL Furnish and Install: Tele-data, WAPS (pull wires only), Floor Boxes, </t>
     </r>
@@ -623,7 +718,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Included in above number)</t>
     </r>
@@ -634,7 +728,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">ELECTRICAL CCTV - wires supplied by owners vendor, GC to pull, termination by vendor </t>
     </r>
@@ -644,7 +737,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Included in above number)</t>
     </r>
@@ -655,7 +747,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">ELECTRICAL AV - speaker and wire supplied by owner's vendor, GC to install speaker and pull wire, termination by vendor </t>
     </r>
@@ -665,7 +756,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Included in above number)</t>
     </r>
@@ -676,7 +766,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Shopper tracker_ Cabling by GC (termination by owner vendor ) </t>
     </r>
@@ -686,7 +775,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Included in above number)</t>
     </r>
@@ -697,7 +785,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>EAS_ Cabling by GC (termination by vendor) coordination by GC</t>
     </r>
@@ -707,7 +794,6 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> (Included in above number)</t>
     </r>
@@ -717,12 +803,6 @@
   </si>
   <si>
     <t xml:space="preserve">Electrical permit and fees </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical testing and commissioning </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smart meter_ Provided by owner vendor installed by GC </t>
   </si>
   <si>
     <r>
@@ -730,7 +810,34 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Electrical testing and commissioning </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(Intertek UL Certification)</t>
+    </r>
+  </si>
+  <si>
+    <t>UL Certification of low voltage lighting installed in millwork fixtures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smart meter_ Provided by owner vendor installed by GC </t>
+  </si>
+  <si>
+    <t>Install included in Electrical cost above, supply of smart meter by Owners Vendor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Fire Alarm </t>
     </r>
@@ -740,109 +847,17 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Includes putting the system in test during install)</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Permits and Fees for Fire Alarm </t>
-  </si>
-  <si>
-    <t>SUBTOTAL</t>
-  </si>
-  <si>
-    <t>GENERAL CONTRACTOR COSTS</t>
-  </si>
-  <si>
-    <t>010000</t>
-  </si>
-  <si>
-    <t>General Conditions to include:</t>
-  </si>
-  <si>
-    <t>Project Executive</t>
-  </si>
-  <si>
-    <t>Project Manager</t>
-  </si>
-  <si>
-    <t>Weeks</t>
-  </si>
-  <si>
-    <t>Site Super</t>
-  </si>
-  <si>
-    <t>Site Laborer</t>
-  </si>
-  <si>
-    <t>4@2000</t>
-  </si>
-  <si>
-    <t>4@4000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field Staff Expenses (travel lodging, reimbursables) </t>
-  </si>
-  <si>
-    <t>7 visits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operational and head office cost </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAXES </t>
-  </si>
-  <si>
-    <t>OVERHEAD and FEE</t>
-  </si>
-  <si>
-    <t>Markup</t>
-  </si>
-  <si>
-    <t>INSURANCE</t>
-  </si>
-  <si>
-    <t>GRAND TOTAL</t>
-  </si>
-  <si>
-    <t>OTHER MISCELLANEOUS</t>
-  </si>
-  <si>
-    <t>% on Change orders, incl. insurance</t>
-  </si>
-  <si>
-    <t>Additional week of General Conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supervision for Saturday During Millwork Installation </t>
-  </si>
-  <si>
-    <t>Inc.</t>
-  </si>
-  <si>
-    <t>Allowance - Additionl permit fees above allowance will be a pass through expense at no markup</t>
-  </si>
-  <si>
-    <t>UL Listing of exterior signage included below, Millwork UL listing as alternate below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLOOR: Basaltite- 1197mmx11587mm Basaltina Marble Floor Tiles;  </t>
-  </si>
-  <si>
-    <t>Land Lord attic stock tile or stone - Assumes 162 SQFT and $34.00/SQFT for Material</t>
-  </si>
-  <si>
-    <t>Included in framing number below and breakout numbers below</t>
-  </si>
-  <si>
-    <t>Add Alternate - Security mesh at corridor demising wall</t>
-  </si>
-  <si>
-    <t>Add Alternate - UL Certifaction of Millwork Only</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
       <t xml:space="preserve">Shop drawings and Coordination up to 3 revisions </t>
     </r>
     <r>
@@ -851,91 +866,108 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>(Included in fire alarm pricing above)</t>
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">ELECTRICAL Lighting drivers; Furnish and Install ALL in scope of work </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(114 drivers includes 5 spares)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Internal Doors Hardware and  Lockset Supply and Install </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Door #08 and Door to unusable space)</t>
-    </r>
+    <t xml:space="preserve">Permits and Fees for Fire Alarm </t>
+  </si>
+  <si>
+    <t>SUBTOTAL</t>
+  </si>
+  <si>
+    <t>GENERAL CONTRACTOR COSTS</t>
+  </si>
+  <si>
+    <t>010000</t>
+  </si>
+  <si>
+    <t>General Conditions to include:</t>
+  </si>
+  <si>
+    <t>Project Executive</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Weeks</t>
+  </si>
+  <si>
+    <t>Site Super</t>
+  </si>
+  <si>
+    <t>Site Laborer</t>
+  </si>
+  <si>
+    <t>4@2000</t>
+  </si>
+  <si>
+    <t>4@4000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field Staff Expenses (travel lodging, reimbursables) </t>
+  </si>
+  <si>
+    <t>7 visits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operational and head office cost </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAXES </t>
+  </si>
+  <si>
+    <t>OVERHEAD and FEE</t>
+  </si>
+  <si>
+    <t>Markup</t>
+  </si>
+  <si>
+    <t>INSURANCE</t>
+  </si>
+  <si>
+    <t>GRAND TOTAL</t>
   </si>
   <si>
     <t>This proposal excludes all governmental taxes, development charges, impact fees, utility fees, and other jurisdictional assessments unless specifically noted otherwise.</t>
   </si>
   <si>
-    <t>LBC holds each sub to daily cleaning before they leave so this is covered in the bid</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Barricade installation and Removal + Coordination of installation of Barricade Graphic  (include making good LL finishes including LL tiles, transitions and finishes) - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Touch up finishes after barricade is removed and Barricade rental.  Barricade graphics are to be supplied by Celine</t>
-    </r>
-  </si>
-  <si>
-    <t>Samples including level 5 drywall finish are included</t>
-  </si>
-  <si>
-    <t>Revised per request from Celine - Storage and Receiving</t>
-  </si>
-  <si>
-    <t>5 point electrified lock and entry doors included in pricing</t>
-  </si>
-  <si>
-    <t>Level 5 finish mock up requested by Celine - Included in price and confrimed by subcontractor</t>
-  </si>
-  <si>
-    <t>Add Alternate - Louis Hoffman Storefront</t>
-  </si>
-  <si>
-    <t>Install for Landlord attic stock tile listed below</t>
-  </si>
-  <si>
-    <t>Supply of Landlord attic stock tile - 4 courses of tile</t>
-  </si>
-  <si>
-    <t>Add Alternate - Louis Hoffman Storefront - Single Piece Glass</t>
-  </si>
-  <si>
-    <t>On top of LBC price listed in Line 86 above</t>
-  </si>
-  <si>
-    <t>Large window is estimated at 3 pieces of glass, this would be an add to have an oversized single piece of glass</t>
+    <t>OTHER MISCELLANEOUS</t>
+  </si>
+  <si>
+    <t>% on Change orders, incl. insurance</t>
+  </si>
+  <si>
+    <t>Additional week of General Conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supervision for Saturday During Millwork Installation </t>
+  </si>
+  <si>
+    <t>Inc.</t>
+  </si>
+  <si>
+    <t>Add Alternate - Security mesh at corridor demising wall</t>
+  </si>
+  <si>
+    <t>04/09/2026 - Permit Revision 1</t>
+  </si>
+  <si>
+    <t>UL Listing of exterior signage included below, Millwork UL included in Division 18 below</t>
+  </si>
+  <si>
+    <t>Added ACT per revised drawings</t>
+  </si>
+  <si>
+    <t>Added drywall ceiling and framing in new BOH room per revised drawings</t>
+  </si>
+  <si>
+    <t>VCT Floor quoted not sheet goods</t>
+  </si>
+  <si>
+    <t>Reduced per plan revisions 4/9/26</t>
   </si>
 </sst>
 </file>
@@ -950,7 +982,7 @@
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -961,122 +993,114 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1086,9 +1110,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -1125,6 +1149,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF000000"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -1149,18 +1179,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1168,19 +1186,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF00FFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor theme="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor theme="0"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1495,309 +1519,317 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="14" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="16" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="14" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="5" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="22" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="22" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="22" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="24" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="24" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2055,7 +2087,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:Z997"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" customWidth="1"/>
@@ -2109,7 +2141,7 @@
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
     </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="9" t="s">
         <v>0</v>
@@ -2157,11 +2189,11 @@
       <c r="E4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="17">
-        <v>46003</v>
+      <c r="F4" s="143" t="s">
+        <v>213</v>
       </c>
       <c r="G4" s="16"/>
-      <c r="H4" s="18"/>
+      <c r="H4" s="17"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -2183,21 +2215,21 @@
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="15"/>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="19" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="20" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="16"/>
-      <c r="H5" s="18"/>
+      <c r="H5" s="17"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -2219,17 +2251,17 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
-      <c r="B6" s="22"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="22">
         <v>46031</v>
       </c>
       <c r="G6" s="16"/>
-      <c r="H6" s="18"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -2251,13 +2283,13 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="28"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="27"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -2283,7 +2315,7 @@
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
-      <c r="F8" s="29"/>
+      <c r="F8" s="28"/>
       <c r="G8" s="8"/>
       <c r="H8" s="16"/>
       <c r="I8" s="4"/>
@@ -2307,13 +2339,13 @@
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="29" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="31"/>
+      <c r="F9" s="30"/>
       <c r="G9" s="8"/>
       <c r="H9" s="16"/>
       <c r="I9" s="4"/>
@@ -2337,15 +2369,15 @@
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="34" t="s">
+      <c r="B10" s="31"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="35"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="34"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="33"/>
+      <c r="H10" s="32"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -2367,15 +2399,15 @@
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="34" t="s">
+      <c r="B11" s="31"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="37"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="36"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="36"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -2396,363 +2428,375 @@
       <c r="Z11" s="4"/>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="38"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="34" t="s">
+      <c r="B12" s="37"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="37"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="36"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="36"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="38"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="34" t="s">
+      <c r="B13" s="37"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="36"/>
-      <c r="F13" s="37"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="36"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="36"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="38"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="40" t="s">
+      <c r="B14" s="37"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="37"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="36"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="36"/>
+      <c r="H14" s="35"/>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="41" t="s">
+      <c r="B15" s="37"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="43"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="42"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="42"/>
+      <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="34" t="s">
+      <c r="B16" s="37"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="42"/>
-      <c r="F16" s="43"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="42"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="42"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="141"/>
-      <c r="C17" s="131"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
+      <c r="B17" s="142"/>
+      <c r="C17" s="132"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="35"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="32"/>
+      <c r="H18" s="31"/>
     </row>
     <row r="19" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="32"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="44" t="s">
+      <c r="B19" s="31"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="45" t="s">
+      <c r="F19" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="46" t="s">
+      <c r="G19" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="H19" s="47" t="s">
+      <c r="H19" s="46" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48"/>
-      <c r="B20" s="138" t="s">
+      <c r="A20" s="47"/>
+      <c r="B20" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="136"/>
-      <c r="D20" s="137"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="50" t="s">
+      <c r="C20" s="137"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="G20" s="51"/>
-      <c r="H20" s="49">
+      <c r="G20" s="50"/>
+      <c r="H20" s="48">
         <f>SUM(H21:H34)</f>
-        <v>63555</v>
-      </c>
-      <c r="I20" s="52"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="48"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="48"/>
-      <c r="P20" s="48"/>
-      <c r="Q20" s="48"/>
-      <c r="R20" s="48"/>
-      <c r="S20" s="48"/>
-      <c r="T20" s="48"/>
-      <c r="U20" s="48"/>
-      <c r="V20" s="48"/>
-      <c r="W20" s="48"/>
-      <c r="X20" s="48"/>
-      <c r="Y20" s="48"/>
-      <c r="Z20" s="48"/>
-    </row>
-    <row r="21" spans="1:26" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="53"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="54" t="s">
-        <v>200</v>
+        <v>64575</v>
+      </c>
+      <c r="I20" s="51"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="47"/>
+      <c r="V20" s="47"/>
+      <c r="W20" s="47"/>
+      <c r="X20" s="47"/>
+      <c r="Y20" s="47"/>
+      <c r="Z20" s="47"/>
+    </row>
+    <row r="21" spans="1:26" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="52"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="53" t="s">
+        <v>27</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="56">
+      <c r="G21" s="54"/>
+      <c r="H21" s="55">
         <v>13583</v>
       </c>
-      <c r="I21" s="57"/>
+      <c r="I21" s="56"/>
     </row>
     <row r="22" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="53"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39" t="s">
-        <v>27</v>
+      <c r="B22" s="52"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38" t="s">
+        <v>28</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="56">
+      <c r="G22" s="57"/>
+      <c r="H22" s="55">
         <v>0</v>
       </c>
-      <c r="I22" s="142" t="s">
-        <v>199</v>
-      </c>
-      <c r="J22" s="121"/>
-      <c r="K22" s="121"/>
-      <c r="L22" s="121"/>
-      <c r="M22" s="121"/>
-      <c r="N22" s="121"/>
-      <c r="O22" s="121"/>
+      <c r="I22" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="J22" s="58"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="58"/>
+      <c r="O22" s="58"/>
     </row>
     <row r="23" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="53"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39" t="s">
-        <v>28</v>
+      <c r="B23" s="52"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58">
-        <v>7830</v>
-      </c>
-      <c r="I23" s="59"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57">
+        <v>8850</v>
+      </c>
+      <c r="I23" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="61"/>
     </row>
     <row r="24" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="53"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39" t="s">
-        <v>29</v>
+      <c r="B24" s="52"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38" t="s">
+        <v>32</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="56">
+      <c r="G24" s="57"/>
+      <c r="H24" s="55">
         <v>10000</v>
       </c>
-      <c r="I24" s="60" t="s">
-        <v>188</v>
-      </c>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="61"/>
+      <c r="I24" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="63"/>
+      <c r="K24" s="63"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="61"/>
+      <c r="O24" s="146"/>
+      <c r="P24" s="145"/>
+      <c r="Q24" s="145"/>
     </row>
     <row r="25" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="53"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39" t="s">
-        <v>30</v>
+      <c r="B25" s="52"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38" t="s">
+        <v>34</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58">
-        <f t="shared" ref="H25" si="0">E25*G25</f>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57">
+        <f>E25*G25</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="53"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39" t="s">
-        <v>31</v>
+      <c r="B26" s="52"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="56">
+      <c r="F26" s="34"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="55">
         <v>3950</v>
       </c>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="62"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="64"/>
     </row>
     <row r="27" spans="1:26" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="53"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="54" t="s">
-        <v>32</v>
+      <c r="B27" s="52"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="53" t="s">
+        <v>36</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58">
+      <c r="F27" s="34"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57">
         <v>6500</v>
       </c>
-      <c r="I27" s="63"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="62"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="66"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="64"/>
     </row>
     <row r="28" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="53"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="54" t="s">
-        <v>33</v>
+      <c r="B28" s="52"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="53" t="s">
+        <v>37</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="56">
+      <c r="F28" s="34"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="55">
         <v>6425</v>
       </c>
-      <c r="I28" s="119"/>
-      <c r="J28" s="120"/>
-      <c r="K28" s="115"/>
-      <c r="L28" s="115"/>
-      <c r="M28" s="115"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="67"/>
+      <c r="M28" s="67"/>
     </row>
     <row r="29" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="53"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39" t="s">
-        <v>34</v>
+      <c r="B29" s="52"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38" t="s">
+        <v>38</v>
       </c>
       <c r="E29" s="2"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="56">
+      <c r="F29" s="34"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="55">
         <v>4730</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="53"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="54" t="s">
-        <v>35</v>
+      <c r="B30" s="52"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="53" t="s">
+        <v>39</v>
       </c>
       <c r="E30" s="2"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="56">
+      <c r="F30" s="34"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="55">
         <v>2800</v>
       </c>
-      <c r="I30" s="65"/>
+      <c r="I30" s="69"/>
     </row>
     <row r="31" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="53"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="54" t="s">
-        <v>36</v>
+      <c r="B31" s="52"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="53" t="s">
+        <v>40</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58">
+      <c r="F31" s="34"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57">
         <v>3862</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="53"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39" t="s">
-        <v>37</v>
+      <c r="B32" s="52"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38" t="s">
+        <v>41</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58">
+      <c r="F32" s="34"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57">
         <v>3875</v>
       </c>
-      <c r="I32" s="65"/>
+      <c r="I32" s="69"/>
     </row>
     <row r="33" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="53"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39" t="s">
-        <v>38</v>
+      <c r="B33" s="52"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38" t="s">
+        <v>42</v>
       </c>
       <c r="E33" s="2"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="56">
+      <c r="F33" s="34"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="55">
         <v>0</v>
       </c>
-      <c r="I33" s="116" t="s">
-        <v>189</v>
-      </c>
-      <c r="J33" s="117"/>
-      <c r="K33" s="117"/>
-      <c r="L33" s="117"/>
-      <c r="M33" s="117"/>
-      <c r="N33" s="118"/>
-      <c r="O33" s="118"/>
+      <c r="I33" s="144" t="s">
+        <v>214</v>
+      </c>
+      <c r="J33" s="70"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="70"/>
+      <c r="O33" s="70"/>
+      <c r="P33" s="145"/>
     </row>
     <row r="34" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="53"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39" t="s">
-        <v>39</v>
+      <c r="B34" s="52"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38" t="s">
+        <v>43</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="35"/>
+      <c r="F34" s="34"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="58">
+      <c r="H34" s="57">
         <f>E34*G34</f>
         <v>0</v>
       </c>
-      <c r="I34" s="121" t="s">
-        <v>201</v>
-      </c>
-      <c r="J34" s="121"/>
-      <c r="K34" s="121"/>
-      <c r="L34" s="121"/>
-      <c r="M34" s="121"/>
+      <c r="I34" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" s="58"/>
+      <c r="K34" s="58"/>
+      <c r="L34" s="58"/>
+      <c r="M34" s="58"/>
     </row>
     <row r="35" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
@@ -2760,3155 +2804,3163 @@
       <c r="G35" s="2"/>
     </row>
     <row r="36" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
-      <c r="B36" s="138" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="136"/>
-      <c r="D36" s="137"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="49">
+      <c r="A36" s="47"/>
+      <c r="B36" s="139" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="137"/>
+      <c r="D36" s="138"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="49"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="48">
         <f>H37</f>
-        <v>2785</v>
-      </c>
-      <c r="I36" s="52"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
-      <c r="L36" s="48"/>
-      <c r="M36" s="48"/>
-      <c r="N36" s="48"/>
-      <c r="O36" s="48"/>
-      <c r="P36" s="48"/>
-      <c r="Q36" s="48"/>
-      <c r="R36" s="48"/>
-      <c r="S36" s="48"/>
-      <c r="T36" s="48"/>
-      <c r="U36" s="48"/>
-      <c r="V36" s="48"/>
-      <c r="W36" s="48"/>
-      <c r="X36" s="48"/>
-      <c r="Y36" s="48"/>
-      <c r="Z36" s="48"/>
+        <v>5785</v>
+      </c>
+      <c r="I36" s="51"/>
+      <c r="J36" s="47"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="47"/>
+      <c r="M36" s="47"/>
+      <c r="N36" s="47"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="47"/>
+      <c r="Q36" s="47"/>
+      <c r="R36" s="47"/>
+      <c r="S36" s="47"/>
+      <c r="T36" s="47"/>
+      <c r="U36" s="47"/>
+      <c r="V36" s="47"/>
+      <c r="W36" s="47"/>
+      <c r="X36" s="47"/>
+      <c r="Y36" s="47"/>
+      <c r="Z36" s="47"/>
     </row>
     <row r="37" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="53"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="32" t="s">
-        <v>41</v>
+      <c r="B37" s="52"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="31" t="s">
+        <v>46</v>
       </c>
       <c r="E37" s="2"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="56">
-        <v>2785</v>
-      </c>
-      <c r="I37" s="66"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="55">
+        <v>5785</v>
+      </c>
+      <c r="I37" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="J37" s="60"/>
+      <c r="K37" s="60"/>
+      <c r="L37" s="60"/>
+      <c r="M37" s="60"/>
+      <c r="N37" s="60"/>
+      <c r="O37" s="60"/>
+      <c r="P37" s="61"/>
+      <c r="Q37" s="61"/>
+      <c r="R37" s="61"/>
+      <c r="S37" s="61"/>
+      <c r="T37" s="61"/>
+      <c r="U37" s="61"/>
     </row>
     <row r="38" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="53"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="32"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="31"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="35"/>
+      <c r="F38" s="34"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="58"/>
+      <c r="H38" s="57"/>
     </row>
     <row r="39" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
-      <c r="B39" s="138" t="s">
-        <v>42</v>
-      </c>
-      <c r="C39" s="136"/>
-      <c r="D39" s="137"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="49">
+      <c r="A39" s="47"/>
+      <c r="B39" s="139" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="137"/>
+      <c r="D39" s="138"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="48">
         <f>SUM(H40:H46)</f>
         <v>55666</v>
       </c>
-      <c r="I39" s="52"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
-      <c r="L39" s="66"/>
-      <c r="M39" s="48"/>
-      <c r="N39" s="48"/>
-      <c r="O39" s="48"/>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="48"/>
-      <c r="R39" s="48"/>
-      <c r="S39" s="48"/>
-      <c r="T39" s="48"/>
-      <c r="U39" s="48"/>
-      <c r="V39" s="48"/>
-      <c r="W39" s="48"/>
-      <c r="X39" s="48"/>
-      <c r="Y39" s="48"/>
-      <c r="Z39" s="48"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="47"/>
+      <c r="K39" s="47"/>
+      <c r="L39" s="72"/>
+      <c r="M39" s="47"/>
+      <c r="N39" s="47"/>
+      <c r="O39" s="47"/>
+      <c r="P39" s="47"/>
+      <c r="Q39" s="47"/>
+      <c r="R39" s="47"/>
+      <c r="S39" s="47"/>
+      <c r="T39" s="47"/>
+      <c r="U39" s="47"/>
+      <c r="V39" s="47"/>
+      <c r="W39" s="47"/>
+      <c r="X39" s="47"/>
+      <c r="Y39" s="47"/>
+      <c r="Z39" s="47"/>
     </row>
     <row r="40" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="53"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="32" t="s">
-        <v>43</v>
+      <c r="B40" s="52"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="31" t="s">
+        <v>49</v>
       </c>
       <c r="E40" s="2"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58">
+      <c r="F40" s="34"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57">
         <v>2400</v>
       </c>
-      <c r="I40" s="66"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="66"/>
-      <c r="L40" s="66"/>
-      <c r="M40" s="66"/>
+      <c r="I40" s="72"/>
+      <c r="J40" s="72"/>
+      <c r="K40" s="72"/>
+      <c r="L40" s="72"/>
+      <c r="M40" s="72"/>
     </row>
     <row r="41" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="53"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="32" t="s">
-        <v>44</v>
+      <c r="B41" s="52"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="31" t="s">
+        <v>50</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58">
+      <c r="F41" s="34"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57">
         <f>E41*G41</f>
         <v>0</v>
       </c>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="66"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="72"/>
+      <c r="K41" s="72"/>
+      <c r="L41" s="72"/>
+      <c r="M41" s="72"/>
     </row>
     <row r="42" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="53"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="32" t="s">
-        <v>45</v>
+      <c r="B42" s="52"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="31" t="s">
+        <v>51</v>
       </c>
       <c r="E42" s="2"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58">
+      <c r="F42" s="34"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57">
         <v>13845</v>
       </c>
-      <c r="I42" s="66"/>
-      <c r="J42" s="66"/>
-      <c r="K42" s="66"/>
-      <c r="L42" s="66"/>
-      <c r="M42" s="66"/>
+      <c r="I42" s="72"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="72"/>
+      <c r="M42" s="72"/>
     </row>
     <row r="43" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="53"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="32" t="s">
-        <v>46</v>
+      <c r="B43" s="52"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="31" t="s">
+        <v>52</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="56">
+      <c r="F43" s="34"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="55">
         <v>6750</v>
       </c>
-      <c r="I43" s="66"/>
-      <c r="J43" s="66"/>
-      <c r="K43" s="66"/>
-      <c r="L43" s="66"/>
-      <c r="M43" s="66"/>
+      <c r="I43" s="72"/>
+      <c r="J43" s="72"/>
+      <c r="K43" s="72"/>
+      <c r="L43" s="72"/>
+      <c r="M43" s="72"/>
     </row>
     <row r="44" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="53"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="32" t="s">
-        <v>47</v>
+      <c r="B44" s="52"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="31" t="s">
+        <v>53</v>
       </c>
       <c r="E44" s="2"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="56">
+      <c r="F44" s="34"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="55">
         <v>24600</v>
       </c>
-      <c r="I44" s="66"/>
-      <c r="J44" s="66"/>
-      <c r="K44" s="66"/>
-      <c r="L44" s="66"/>
-      <c r="M44" s="66"/>
+      <c r="I44" s="72"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="72"/>
+      <c r="M44" s="72"/>
     </row>
     <row r="45" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="53"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="32" t="s">
-        <v>48</v>
+      <c r="B45" s="52"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="31" t="s">
+        <v>54</v>
       </c>
       <c r="E45" s="2"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="56">
+      <c r="F45" s="34"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="55">
         <v>3271</v>
       </c>
-      <c r="I45" s="66"/>
-      <c r="J45" s="66"/>
-      <c r="K45" s="66"/>
-      <c r="L45" s="66"/>
-      <c r="M45" s="66"/>
+      <c r="I45" s="72"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="72"/>
+      <c r="L45" s="72"/>
+      <c r="M45" s="72"/>
     </row>
     <row r="46" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="53"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="32" t="s">
-        <v>49</v>
+      <c r="B46" s="52"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="31" t="s">
+        <v>55</v>
       </c>
       <c r="E46" s="2"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="56">
+      <c r="F46" s="34"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="55">
         <v>4800</v>
       </c>
-      <c r="I46" s="66"/>
-      <c r="J46" s="66"/>
-      <c r="K46" s="66"/>
-      <c r="L46" s="66"/>
-      <c r="M46" s="66"/>
+      <c r="I46" s="72"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="72"/>
+      <c r="M46" s="72"/>
     </row>
     <row r="47" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="53"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="32"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="31"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="35"/>
+      <c r="F47" s="34"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="66"/>
-      <c r="J47" s="66"/>
-      <c r="K47" s="66"/>
-      <c r="L47" s="66"/>
-      <c r="M47" s="66"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="72"/>
+      <c r="J47" s="72"/>
+      <c r="K47" s="72"/>
+      <c r="L47" s="72"/>
+      <c r="M47" s="72"/>
     </row>
     <row r="48" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="48"/>
-      <c r="B48" s="138" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="136"/>
-      <c r="D48" s="137"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="49">
+      <c r="A48" s="47"/>
+      <c r="B48" s="139" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="137"/>
+      <c r="D48" s="138"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="50"/>
+      <c r="H48" s="48">
         <f>SUM(H49:H53)</f>
         <v>65625</v>
       </c>
-      <c r="I48" s="52"/>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
-      <c r="L48" s="48"/>
-      <c r="M48" s="48"/>
-      <c r="N48" s="48"/>
-      <c r="O48" s="48"/>
-      <c r="P48" s="48"/>
-      <c r="Q48" s="48"/>
-      <c r="R48" s="48"/>
-      <c r="S48" s="48"/>
-      <c r="T48" s="48"/>
-      <c r="U48" s="48"/>
-      <c r="V48" s="48"/>
-      <c r="W48" s="48"/>
-      <c r="X48" s="48"/>
-      <c r="Y48" s="48"/>
-      <c r="Z48" s="48"/>
+      <c r="I48" s="51"/>
+      <c r="J48" s="47"/>
+      <c r="K48" s="47"/>
+      <c r="L48" s="47"/>
+      <c r="M48" s="47"/>
+      <c r="N48" s="47"/>
+      <c r="O48" s="47"/>
+      <c r="P48" s="47"/>
+      <c r="Q48" s="47"/>
+      <c r="R48" s="47"/>
+      <c r="S48" s="47"/>
+      <c r="T48" s="47"/>
+      <c r="U48" s="47"/>
+      <c r="V48" s="47"/>
+      <c r="W48" s="47"/>
+      <c r="X48" s="47"/>
+      <c r="Y48" s="47"/>
+      <c r="Z48" s="47"/>
     </row>
     <row r="49" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="53"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="67" t="s">
-        <v>51</v>
+      <c r="B49" s="52"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="73" t="s">
+        <v>57</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="68"/>
-      <c r="H49" s="58">
+      <c r="F49" s="34"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="57">
         <v>48000</v>
       </c>
-      <c r="I49" s="68"/>
+      <c r="I49" s="74"/>
     </row>
     <row r="50" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="53"/>
-      <c r="C50" s="39"/>
-      <c r="D50" s="67" t="s">
-        <v>52</v>
+      <c r="B50" s="52"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="73" t="s">
+        <v>58</v>
       </c>
       <c r="E50" s="2"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="69"/>
-      <c r="H50" s="58">
+      <c r="F50" s="34"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="57">
         <v>7325</v>
       </c>
-      <c r="I50" s="143" t="s">
-        <v>202</v>
-      </c>
-      <c r="J50" s="117"/>
-      <c r="K50" s="117"/>
-      <c r="L50" s="144"/>
-      <c r="M50" s="118"/>
+      <c r="I50" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="J50" s="70"/>
+      <c r="K50" s="70"/>
+      <c r="L50" s="70"/>
+      <c r="M50" s="70"/>
     </row>
     <row r="51" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="53"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="67" t="s">
-        <v>53</v>
+      <c r="B51" s="52"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="73" t="s">
+        <v>60</v>
       </c>
       <c r="E51" s="2"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="69"/>
-      <c r="H51" s="56">
+      <c r="F51" s="34"/>
+      <c r="G51" s="75"/>
+      <c r="H51" s="55">
         <v>500</v>
       </c>
-      <c r="I51" s="66"/>
+      <c r="I51" s="72"/>
     </row>
     <row r="52" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="53"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="32" t="s">
-        <v>190</v>
+      <c r="B52" s="52"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="31" t="s">
+        <v>61</v>
       </c>
       <c r="E52" s="2"/>
-      <c r="F52" s="70"/>
-      <c r="H52" s="56">
+      <c r="F52" s="77"/>
+      <c r="H52" s="55">
         <v>4292</v>
       </c>
-      <c r="I52" s="145" t="s">
-        <v>206</v>
-      </c>
-      <c r="J52" s="145"/>
-      <c r="K52" s="145"/>
-      <c r="L52" s="145"/>
-      <c r="M52" s="147"/>
-      <c r="N52" s="147"/>
+      <c r="I52" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="J52" s="78"/>
+      <c r="K52" s="78"/>
+      <c r="L52" s="78"/>
+      <c r="M52" s="79"/>
+      <c r="N52" s="79"/>
     </row>
     <row r="53" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="53"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="32" t="s">
-        <v>191</v>
+      <c r="B53" s="52"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="31" t="s">
+        <v>63</v>
       </c>
       <c r="E53" s="2"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="58">
+      <c r="F53" s="34"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57">
         <v>5508</v>
       </c>
-      <c r="I53" s="145" t="s">
-        <v>207</v>
-      </c>
-      <c r="J53" s="121"/>
-      <c r="K53" s="121"/>
-      <c r="L53" s="121"/>
-      <c r="M53" s="121"/>
+      <c r="I53" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="J53" s="58"/>
+      <c r="K53" s="58"/>
+      <c r="L53" s="58"/>
+      <c r="M53" s="58"/>
     </row>
     <row r="54" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="53"/>
-      <c r="C54" s="39"/>
-      <c r="D54" s="32"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="31"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="35"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="58"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="57"/>
     </row>
     <row r="55" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="48"/>
-      <c r="B55" s="138" t="s">
-        <v>54</v>
-      </c>
-      <c r="C55" s="136"/>
-      <c r="D55" s="137"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="50"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="49">
+      <c r="A55" s="47"/>
+      <c r="B55" s="139" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="137"/>
+      <c r="D55" s="138"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="50"/>
+      <c r="H55" s="48">
         <f>SUM(H56:H65)</f>
         <v>19185</v>
       </c>
-      <c r="I55" s="52"/>
-      <c r="J55" s="48"/>
-      <c r="K55" s="48"/>
-      <c r="L55" s="48"/>
-      <c r="M55" s="48"/>
-      <c r="N55" s="48"/>
-      <c r="O55" s="48"/>
-      <c r="P55" s="48"/>
-      <c r="Q55" s="48"/>
-      <c r="R55" s="48"/>
-      <c r="S55" s="48"/>
-      <c r="T55" s="48"/>
-      <c r="U55" s="48"/>
-      <c r="V55" s="48"/>
-      <c r="W55" s="48"/>
-      <c r="X55" s="48"/>
-      <c r="Y55" s="48"/>
-      <c r="Z55" s="48"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="47"/>
+      <c r="K55" s="47"/>
+      <c r="L55" s="47"/>
+      <c r="M55" s="47"/>
+      <c r="N55" s="47"/>
+      <c r="O55" s="47"/>
+      <c r="P55" s="47"/>
+      <c r="Q55" s="47"/>
+      <c r="R55" s="47"/>
+      <c r="S55" s="47"/>
+      <c r="T55" s="47"/>
+      <c r="U55" s="47"/>
+      <c r="V55" s="47"/>
+      <c r="W55" s="47"/>
+      <c r="X55" s="47"/>
+      <c r="Y55" s="47"/>
+      <c r="Z55" s="47"/>
     </row>
     <row r="56" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="53"/>
-      <c r="C56" s="39"/>
-      <c r="D56" s="32" t="s">
-        <v>55</v>
+      <c r="B56" s="52"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="E56" s="2"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="58"/>
-      <c r="H56" s="58">
-        <f t="shared" ref="H56:H64" si="1">E56*G56</f>
+      <c r="F56" s="34"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57">
+        <f t="shared" ref="H56:H58" si="0">E56*G56</f>
         <v>0</v>
       </c>
-      <c r="I56" s="62"/>
-      <c r="J56" s="62"/>
-      <c r="K56" s="62"/>
+      <c r="I56" s="64"/>
+      <c r="J56" s="64"/>
+      <c r="K56" s="64"/>
     </row>
     <row r="57" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="53"/>
-      <c r="C57" s="39"/>
-      <c r="D57" s="32" t="s">
-        <v>56</v>
+      <c r="B57" s="52"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="E57" s="2"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="58"/>
-      <c r="H57" s="58">
+      <c r="F57" s="34"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="52"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="52"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="151">
+        <v>19185</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="52"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57">
+        <f t="shared" ref="H60:H64" si="1">E60*G60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="52"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="57"/>
+      <c r="H61" s="57">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="53"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="58"/>
-      <c r="H58" s="58">
+    <row r="62" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="52"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="57">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="53"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="58"/>
-      <c r="H59" s="58">
-        <v>19185</v>
-      </c>
-    </row>
-    <row r="60" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="53"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="58"/>
-      <c r="H60" s="58">
+    <row r="63" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="52"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="57"/>
+      <c r="H63" s="57">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="53"/>
-      <c r="C61" s="39"/>
-      <c r="D61" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="58"/>
-      <c r="H61" s="58">
+    <row r="64" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="52"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="53"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="58">
-        <f t="shared" si="1"/>
+    <row r="65" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="52"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="57"/>
+    </row>
+    <row r="66" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="47"/>
+      <c r="B66" s="139" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" s="137"/>
+      <c r="D66" s="138"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="50"/>
+      <c r="H66" s="48">
+        <f>SUM(H67:H72)</f>
+        <v>46220</v>
+      </c>
+      <c r="I66" s="51"/>
+      <c r="J66" s="47"/>
+      <c r="K66" s="47"/>
+      <c r="L66" s="47"/>
+      <c r="M66" s="47"/>
+      <c r="N66" s="47"/>
+      <c r="O66" s="47"/>
+      <c r="P66" s="47"/>
+      <c r="Q66" s="47"/>
+      <c r="R66" s="47"/>
+      <c r="S66" s="47"/>
+      <c r="T66" s="47"/>
+      <c r="U66" s="47"/>
+      <c r="V66" s="47"/>
+      <c r="W66" s="47"/>
+      <c r="X66" s="47"/>
+      <c r="Y66" s="47"/>
+      <c r="Z66" s="47"/>
+    </row>
+    <row r="67" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="52"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" s="34"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="53"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="58">
-        <f t="shared" si="1"/>
+      <c r="I67" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J67" s="70"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="70"/>
+      <c r="M67" s="70"/>
+      <c r="N67" s="70"/>
+    </row>
+    <row r="68" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="52"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" s="34"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="151">
+        <v>3685</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="52"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" s="34"/>
+      <c r="G69" s="57"/>
+      <c r="H69" s="151">
+        <v>5875</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="52"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" s="34"/>
+      <c r="G70" s="57"/>
+      <c r="H70" s="147">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="53"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="58"/>
-      <c r="H64" s="58">
-        <f t="shared" si="1"/>
+      <c r="I70" s="152"/>
+      <c r="J70" s="152"/>
+      <c r="K70" s="152"/>
+      <c r="L70" s="152"/>
+    </row>
+    <row r="71" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="52"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="57"/>
+      <c r="H71" s="57">
+        <v>36660</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="52"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="53"/>
-      <c r="C65" s="39"/>
-      <c r="D65" s="32"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="58"/>
-    </row>
-    <row r="66" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="48"/>
-      <c r="B66" s="138" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" s="136"/>
-      <c r="D66" s="137"/>
-      <c r="E66" s="49"/>
-      <c r="F66" s="50"/>
-      <c r="G66" s="51"/>
-      <c r="H66" s="49">
-        <f>SUM(H67:H72)</f>
-        <v>41720</v>
-      </c>
-      <c r="I66" s="52"/>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
-      <c r="L66" s="48"/>
-      <c r="M66" s="48"/>
-      <c r="N66" s="48"/>
-      <c r="O66" s="48"/>
-      <c r="P66" s="48"/>
-      <c r="Q66" s="48"/>
-      <c r="R66" s="48"/>
-      <c r="S66" s="48"/>
-      <c r="T66" s="48"/>
-      <c r="U66" s="48"/>
-      <c r="V66" s="48"/>
-      <c r="W66" s="48"/>
-      <c r="X66" s="48"/>
-      <c r="Y66" s="48"/>
-      <c r="Z66" s="48"/>
-    </row>
-    <row r="67" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="53"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58">
-        <v>0</v>
-      </c>
-      <c r="I67" s="121" t="s">
-        <v>192</v>
-      </c>
-      <c r="J67" s="118"/>
-      <c r="K67" s="118"/>
-      <c r="L67" s="118"/>
-      <c r="M67" s="118"/>
-      <c r="N67" s="118"/>
-    </row>
-    <row r="68" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="53"/>
-      <c r="C68" s="39"/>
-      <c r="D68" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58">
-        <v>3685</v>
-      </c>
-    </row>
-    <row r="69" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="53"/>
-      <c r="C69" s="39"/>
-      <c r="D69" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" s="35"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="58">
-        <v>5875</v>
-      </c>
-    </row>
-    <row r="70" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="53"/>
-      <c r="C70" s="39"/>
-      <c r="D70" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="58"/>
-      <c r="H70" s="58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="53"/>
-      <c r="C71" s="39"/>
-      <c r="D71" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" s="35"/>
-      <c r="G71" s="58"/>
-      <c r="H71" s="58">
-        <v>32160</v>
-      </c>
-    </row>
-    <row r="72" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="53"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="58"/>
-      <c r="H72" s="58">
-        <v>0</v>
-      </c>
-    </row>
     <row r="73" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="53"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
       <c r="E73" s="2"/>
-      <c r="F73" s="35"/>
+      <c r="F73" s="34"/>
       <c r="G73" s="2"/>
-      <c r="H73" s="58"/>
+      <c r="H73" s="57"/>
     </row>
     <row r="74" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="48"/>
-      <c r="B74" s="138" t="s">
-        <v>70</v>
-      </c>
-      <c r="C74" s="136"/>
-      <c r="D74" s="137"/>
-      <c r="E74" s="49"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="51"/>
-      <c r="H74" s="49">
+      <c r="A74" s="47"/>
+      <c r="B74" s="139" t="s">
+        <v>82</v>
+      </c>
+      <c r="C74" s="137"/>
+      <c r="D74" s="138"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="50"/>
+      <c r="H74" s="48">
         <f>SUM(H75:H80)</f>
         <v>14575</v>
       </c>
-      <c r="I74" s="52"/>
-      <c r="J74" s="48"/>
-      <c r="K74" s="48"/>
-      <c r="L74" s="48"/>
-      <c r="M74" s="48"/>
-      <c r="N74" s="48"/>
-      <c r="O74" s="48"/>
-      <c r="P74" s="48"/>
-      <c r="Q74" s="48"/>
-      <c r="R74" s="48"/>
-      <c r="S74" s="48"/>
-      <c r="T74" s="48"/>
-      <c r="U74" s="48"/>
-      <c r="V74" s="48"/>
-      <c r="W74" s="48"/>
-      <c r="X74" s="48"/>
-      <c r="Y74" s="48"/>
-      <c r="Z74" s="48"/>
+      <c r="I74" s="51"/>
+      <c r="J74" s="47"/>
+      <c r="K74" s="47"/>
+      <c r="L74" s="47"/>
+      <c r="M74" s="47"/>
+      <c r="N74" s="47"/>
+      <c r="O74" s="47"/>
+      <c r="P74" s="47"/>
+      <c r="Q74" s="47"/>
+      <c r="R74" s="47"/>
+      <c r="S74" s="47"/>
+      <c r="T74" s="47"/>
+      <c r="U74" s="47"/>
+      <c r="V74" s="47"/>
+      <c r="W74" s="47"/>
+      <c r="X74" s="47"/>
+      <c r="Y74" s="47"/>
+      <c r="Z74" s="47"/>
     </row>
     <row r="75" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="53"/>
-      <c r="C75" s="39"/>
-      <c r="D75" s="32" t="s">
-        <v>71</v>
+      <c r="B75" s="52"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="31" t="s">
+        <v>83</v>
       </c>
       <c r="E75" s="2"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="58"/>
-      <c r="H75" s="58">
+      <c r="F75" s="34"/>
+      <c r="G75" s="57"/>
+      <c r="H75" s="57">
         <f t="shared" ref="H75:H76" si="2">E75*G75</f>
         <v>0</v>
       </c>
-      <c r="I75" s="71"/>
-      <c r="J75" s="66"/>
-      <c r="K75" s="66"/>
-      <c r="L75" s="66"/>
-      <c r="M75" s="66"/>
+      <c r="I75" s="80"/>
+      <c r="J75" s="72"/>
+      <c r="K75" s="72"/>
+      <c r="L75" s="72"/>
+      <c r="M75" s="72"/>
     </row>
     <row r="76" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="53"/>
-      <c r="C76" s="39"/>
-      <c r="D76" s="32" t="s">
-        <v>72</v>
+      <c r="B76" s="52"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="31" t="s">
+        <v>84</v>
       </c>
       <c r="E76" s="2"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="58"/>
-      <c r="H76" s="58">
+      <c r="F76" s="34"/>
+      <c r="G76" s="57"/>
+      <c r="H76" s="57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I76" s="66"/>
-      <c r="J76" s="66"/>
-      <c r="K76" s="66"/>
-      <c r="L76" s="66"/>
-      <c r="M76" s="66"/>
+      <c r="I76" s="72"/>
+      <c r="J76" s="72"/>
+      <c r="K76" s="72"/>
+      <c r="L76" s="72"/>
+      <c r="M76" s="72"/>
     </row>
     <row r="77" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="53"/>
-      <c r="C77" s="39"/>
-      <c r="D77" s="32" t="s">
-        <v>73</v>
+      <c r="B77" s="52"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="31" t="s">
+        <v>85</v>
       </c>
       <c r="E77" s="2"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="58"/>
-      <c r="H77" s="58">
+      <c r="F77" s="34"/>
+      <c r="G77" s="57"/>
+      <c r="H77" s="57">
         <v>8900</v>
       </c>
-      <c r="I77" s="66"/>
-      <c r="J77" s="66"/>
-      <c r="K77" s="66"/>
-      <c r="L77" s="66"/>
-      <c r="M77" s="66"/>
+      <c r="I77" s="72"/>
+      <c r="J77" s="72"/>
+      <c r="K77" s="72"/>
+      <c r="L77" s="72"/>
+      <c r="M77" s="72"/>
     </row>
     <row r="78" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="53"/>
-      <c r="C78" s="39"/>
-      <c r="D78" s="32" t="s">
+      <c r="B78" s="52"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" s="34"/>
+      <c r="G78" s="57"/>
+      <c r="H78" s="55">
+        <v>4750</v>
+      </c>
+      <c r="I78" s="81"/>
+      <c r="J78" s="81"/>
+      <c r="K78" s="81"/>
+      <c r="L78" s="81"/>
+      <c r="M78" s="81"/>
+      <c r="N78" s="64"/>
+    </row>
+    <row r="79" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="52"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" s="34"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="55">
+        <v>925</v>
+      </c>
+      <c r="I79" s="72"/>
+      <c r="J79" s="72"/>
+      <c r="K79" s="72"/>
+      <c r="L79" s="72"/>
+      <c r="M79" s="72"/>
+    </row>
+    <row r="80" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="52"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="E78" s="2"/>
-      <c r="F78" s="35"/>
-      <c r="G78" s="58"/>
-      <c r="H78" s="56">
-        <v>4750</v>
-      </c>
-      <c r="I78" s="72"/>
-      <c r="J78" s="72"/>
-      <c r="K78" s="72"/>
-      <c r="L78" s="72"/>
-      <c r="M78" s="72"/>
-      <c r="N78" s="62"/>
-    </row>
-    <row r="79" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="53"/>
-      <c r="C79" s="39"/>
-      <c r="D79" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="58"/>
-      <c r="H79" s="56">
-        <v>925</v>
-      </c>
-      <c r="I79" s="66"/>
-      <c r="J79" s="66"/>
-      <c r="K79" s="66"/>
-      <c r="L79" s="66"/>
-      <c r="M79" s="66"/>
-    </row>
-    <row r="80" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="53"/>
-      <c r="C80" s="39"/>
-      <c r="D80" s="39" t="s">
-        <v>63</v>
-      </c>
       <c r="E80" s="2"/>
-      <c r="F80" s="35"/>
-      <c r="G80" s="58"/>
-      <c r="H80" s="58">
+      <c r="F80" s="34"/>
+      <c r="G80" s="57"/>
+      <c r="H80" s="57">
         <f>E80*G80</f>
         <v>0</v>
       </c>
-      <c r="I80" s="66"/>
-      <c r="J80" s="66"/>
-      <c r="K80" s="66"/>
-      <c r="L80" s="66"/>
-      <c r="M80" s="66"/>
+      <c r="I80" s="72"/>
+      <c r="J80" s="72"/>
+      <c r="K80" s="72"/>
+      <c r="L80" s="72"/>
+      <c r="M80" s="72"/>
     </row>
     <row r="81" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="53"/>
-      <c r="C81" s="39"/>
-      <c r="D81" s="39"/>
+      <c r="B81" s="52"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
       <c r="E81" s="2"/>
-      <c r="F81" s="35"/>
+      <c r="F81" s="34"/>
       <c r="G81" s="2"/>
-      <c r="H81" s="58"/>
+      <c r="H81" s="57"/>
     </row>
     <row r="82" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="48"/>
-      <c r="B82" s="138" t="s">
-        <v>76</v>
-      </c>
-      <c r="C82" s="136"/>
-      <c r="D82" s="137"/>
-      <c r="E82" s="49"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="51"/>
-      <c r="H82" s="49">
+      <c r="A82" s="47"/>
+      <c r="B82" s="139" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" s="137"/>
+      <c r="D82" s="138"/>
+      <c r="E82" s="48"/>
+      <c r="F82" s="49"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="48">
         <f>SUM(H83:H96)</f>
-        <v>197990</v>
-      </c>
-      <c r="I82" s="52"/>
-      <c r="J82" s="48"/>
-      <c r="K82" s="48"/>
-      <c r="L82" s="48"/>
-      <c r="M82" s="48"/>
-      <c r="N82" s="48"/>
-      <c r="O82" s="48"/>
-      <c r="P82" s="48"/>
-      <c r="Q82" s="48"/>
-      <c r="R82" s="48"/>
-      <c r="S82" s="48"/>
-      <c r="T82" s="48"/>
-      <c r="U82" s="48"/>
-      <c r="V82" s="48"/>
-      <c r="W82" s="48"/>
-      <c r="X82" s="48"/>
-      <c r="Y82" s="48"/>
-      <c r="Z82" s="48"/>
+        <v>204290</v>
+      </c>
+      <c r="I82" s="51"/>
+      <c r="J82" s="47"/>
+      <c r="K82" s="47"/>
+      <c r="L82" s="47"/>
+      <c r="M82" s="47"/>
+      <c r="N82" s="47"/>
+      <c r="O82" s="47"/>
+      <c r="P82" s="47"/>
+      <c r="Q82" s="47"/>
+      <c r="R82" s="47"/>
+      <c r="S82" s="47"/>
+      <c r="T82" s="47"/>
+      <c r="U82" s="47"/>
+      <c r="V82" s="47"/>
+      <c r="W82" s="47"/>
+      <c r="X82" s="47"/>
+      <c r="Y82" s="47"/>
+      <c r="Z82" s="47"/>
     </row>
     <row r="83" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="53"/>
-      <c r="C83" s="39"/>
-      <c r="D83" s="33" t="s">
-        <v>77</v>
+      <c r="B83" s="52"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="32" t="s">
+        <v>89</v>
       </c>
       <c r="E83" s="2"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="58"/>
-      <c r="H83" s="58"/>
-      <c r="I83" s="66"/>
-      <c r="J83" s="66"/>
-      <c r="K83" s="66"/>
-      <c r="L83" s="66"/>
-      <c r="M83" s="66"/>
+      <c r="F83" s="34"/>
+      <c r="G83" s="57"/>
+      <c r="H83" s="57"/>
+      <c r="I83" s="72"/>
+      <c r="J83" s="72"/>
+      <c r="K83" s="72"/>
+      <c r="L83" s="72"/>
+      <c r="M83" s="72"/>
     </row>
     <row r="84" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="53"/>
-      <c r="C84" s="39"/>
-      <c r="D84" s="32" t="s">
-        <v>78</v>
+      <c r="B84" s="52"/>
+      <c r="C84" s="38"/>
+      <c r="D84" s="31" t="s">
+        <v>90</v>
       </c>
       <c r="E84" s="2"/>
-      <c r="F84" s="35"/>
-      <c r="G84" s="58"/>
-      <c r="H84" s="58">
+      <c r="F84" s="34"/>
+      <c r="G84" s="57"/>
+      <c r="H84" s="57">
         <f t="shared" ref="H84:H85" si="3">E84*G84</f>
         <v>0</v>
       </c>
-      <c r="I84" s="66"/>
-      <c r="J84" s="66"/>
-      <c r="K84" s="66"/>
-      <c r="L84" s="66"/>
-      <c r="M84" s="66"/>
+      <c r="I84" s="72"/>
+      <c r="J84" s="72"/>
+      <c r="K84" s="72"/>
+      <c r="L84" s="72"/>
+      <c r="M84" s="72"/>
     </row>
     <row r="85" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="53"/>
-      <c r="C85" s="39"/>
-      <c r="D85" s="73" t="s">
-        <v>79</v>
+      <c r="B85" s="52"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="82" t="s">
+        <v>91</v>
       </c>
       <c r="E85" s="2"/>
-      <c r="F85" s="35"/>
-      <c r="G85" s="58"/>
-      <c r="H85" s="58">
+      <c r="F85" s="34"/>
+      <c r="G85" s="57"/>
+      <c r="H85" s="57">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I85" s="66"/>
-      <c r="J85" s="66"/>
-      <c r="K85" s="66"/>
-      <c r="L85" s="66"/>
-      <c r="M85" s="66"/>
+      <c r="I85" s="72"/>
+      <c r="J85" s="72"/>
+      <c r="K85" s="72"/>
+      <c r="L85" s="72"/>
+      <c r="M85" s="72"/>
     </row>
     <row r="86" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="53"/>
-      <c r="C86" s="39"/>
-      <c r="D86" s="73" t="s">
-        <v>80</v>
+      <c r="B86" s="52"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="82" t="s">
+        <v>92</v>
       </c>
       <c r="E86" s="2"/>
-      <c r="F86" s="74"/>
-      <c r="G86" s="75"/>
-      <c r="H86" s="56">
-        <v>190095</v>
-      </c>
-      <c r="I86" s="145" t="s">
-        <v>203</v>
-      </c>
-      <c r="J86" s="145"/>
-      <c r="K86" s="145"/>
-      <c r="L86" s="145"/>
-      <c r="M86" s="145"/>
+      <c r="F86" s="83"/>
+      <c r="G86" s="84"/>
+      <c r="H86" s="150">
+        <v>194895</v>
+      </c>
+      <c r="I86" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="J86" s="78"/>
+      <c r="K86" s="78"/>
+      <c r="L86" s="79"/>
+      <c r="M86" s="79"/>
     </row>
     <row r="87" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="53"/>
-      <c r="C87" s="39"/>
-      <c r="D87" s="32" t="s">
-        <v>81</v>
+      <c r="B87" s="52"/>
+      <c r="C87" s="38"/>
+      <c r="D87" s="31" t="s">
+        <v>94</v>
       </c>
       <c r="E87" s="2"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="58"/>
-      <c r="H87" s="58">
+      <c r="F87" s="34"/>
+      <c r="G87" s="57"/>
+      <c r="H87" s="57">
         <f t="shared" ref="H87:H93" si="4">E87*G87</f>
         <v>0</v>
       </c>
-      <c r="I87" s="66"/>
-      <c r="J87" s="66"/>
-      <c r="K87" s="66"/>
-      <c r="L87" s="66"/>
-      <c r="M87" s="66"/>
+      <c r="I87" s="72"/>
+      <c r="J87" s="72"/>
+      <c r="K87" s="72"/>
+      <c r="L87" s="72"/>
+      <c r="M87" s="72"/>
     </row>
     <row r="88" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="53"/>
-      <c r="C88" s="39"/>
-      <c r="D88" s="39" t="s">
-        <v>82</v>
+      <c r="B88" s="52"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="38" t="s">
+        <v>95</v>
       </c>
       <c r="E88" s="2"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="58"/>
-      <c r="H88" s="58">
+      <c r="F88" s="34"/>
+      <c r="G88" s="57"/>
+      <c r="H88" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I88" s="66"/>
-      <c r="J88" s="66"/>
-      <c r="K88" s="66"/>
-      <c r="L88" s="66"/>
-      <c r="M88" s="66"/>
+      <c r="I88" s="72"/>
+      <c r="J88" s="72"/>
+      <c r="K88" s="72"/>
+      <c r="L88" s="72"/>
+      <c r="M88" s="72"/>
     </row>
     <row r="89" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="53"/>
-      <c r="C89" s="39"/>
-      <c r="D89" s="39" t="s">
-        <v>83</v>
+      <c r="B89" s="52"/>
+      <c r="C89" s="38"/>
+      <c r="D89" s="38" t="s">
+        <v>96</v>
       </c>
       <c r="E89" s="2"/>
-      <c r="F89" s="35"/>
-      <c r="G89" s="58"/>
-      <c r="H89" s="58">
+      <c r="F89" s="34"/>
+      <c r="G89" s="57"/>
+      <c r="H89" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I89" s="66"/>
-      <c r="J89" s="66"/>
-      <c r="K89" s="66"/>
-      <c r="L89" s="66"/>
-      <c r="M89" s="66"/>
+      <c r="I89" s="72"/>
+      <c r="J89" s="72"/>
+      <c r="K89" s="72"/>
+      <c r="L89" s="72"/>
+      <c r="M89" s="72"/>
     </row>
     <row r="90" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="53"/>
-      <c r="C90" s="39"/>
-      <c r="D90" s="39" t="s">
-        <v>84</v>
+      <c r="B90" s="52"/>
+      <c r="C90" s="38"/>
+      <c r="D90" s="38" t="s">
+        <v>97</v>
       </c>
       <c r="E90" s="2"/>
-      <c r="F90" s="35"/>
-      <c r="G90" s="58"/>
-      <c r="H90" s="58">
+      <c r="F90" s="34"/>
+      <c r="G90" s="57"/>
+      <c r="H90" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I90" s="66"/>
-      <c r="J90" s="66"/>
-      <c r="K90" s="66"/>
-      <c r="L90" s="66"/>
-      <c r="M90" s="66"/>
+      <c r="I90" s="72"/>
+      <c r="J90" s="72"/>
+      <c r="K90" s="72"/>
+      <c r="L90" s="72"/>
+      <c r="M90" s="72"/>
     </row>
     <row r="91" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="53"/>
-      <c r="C91" s="39"/>
-      <c r="D91" s="39" t="s">
-        <v>85</v>
+      <c r="B91" s="52"/>
+      <c r="C91" s="38"/>
+      <c r="D91" s="38" t="s">
+        <v>98</v>
       </c>
       <c r="E91" s="2"/>
-      <c r="F91" s="35"/>
-      <c r="G91" s="58"/>
-      <c r="H91" s="58">
+      <c r="F91" s="34"/>
+      <c r="G91" s="57"/>
+      <c r="H91" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I91" s="66"/>
-      <c r="J91" s="66"/>
-      <c r="K91" s="66"/>
-      <c r="L91" s="66"/>
-      <c r="M91" s="66"/>
+      <c r="I91" s="72"/>
+      <c r="J91" s="72"/>
+      <c r="K91" s="72"/>
+      <c r="L91" s="72"/>
+      <c r="M91" s="72"/>
     </row>
     <row r="92" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="53"/>
-      <c r="C92" s="39"/>
-      <c r="D92" s="39" t="s">
-        <v>86</v>
+      <c r="B92" s="52"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38" t="s">
+        <v>99</v>
       </c>
       <c r="E92" s="2"/>
-      <c r="F92" s="35"/>
-      <c r="G92" s="58"/>
-      <c r="H92" s="58">
+      <c r="F92" s="34"/>
+      <c r="G92" s="57"/>
+      <c r="H92" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I92" s="66"/>
-      <c r="J92" s="66"/>
-      <c r="K92" s="66"/>
-      <c r="L92" s="66"/>
-      <c r="M92" s="66"/>
+      <c r="I92" s="72"/>
+      <c r="J92" s="72"/>
+      <c r="K92" s="72"/>
+      <c r="L92" s="72"/>
+      <c r="M92" s="72"/>
     </row>
     <row r="93" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B93" s="53"/>
-      <c r="C93" s="39"/>
-      <c r="D93" s="39" t="s">
-        <v>87</v>
+      <c r="B93" s="52"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="38" t="s">
+        <v>100</v>
       </c>
       <c r="E93" s="2"/>
-      <c r="F93" s="35"/>
-      <c r="G93" s="58"/>
-      <c r="H93" s="58">
+      <c r="F93" s="34"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I93" s="66"/>
-      <c r="J93" s="66"/>
-      <c r="K93" s="66"/>
-      <c r="L93" s="66"/>
-      <c r="M93" s="66"/>
+      <c r="I93" s="72"/>
+      <c r="J93" s="72"/>
+      <c r="K93" s="72"/>
+      <c r="L93" s="72"/>
+      <c r="M93" s="72"/>
     </row>
     <row r="94" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="53"/>
-      <c r="C94" s="39"/>
-      <c r="D94" s="39"/>
+      <c r="B94" s="52"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38"/>
       <c r="E94" s="2"/>
-      <c r="F94" s="35"/>
-      <c r="G94" s="58"/>
-      <c r="H94" s="58">
+      <c r="F94" s="34"/>
+      <c r="G94" s="57"/>
+      <c r="H94" s="57">
         <v>0</v>
       </c>
-      <c r="I94" s="66"/>
-      <c r="J94" s="66"/>
-      <c r="K94" s="66"/>
-      <c r="L94" s="66"/>
-      <c r="M94" s="66"/>
+      <c r="I94" s="72"/>
+      <c r="J94" s="72"/>
+      <c r="K94" s="72"/>
+      <c r="L94" s="72"/>
+      <c r="M94" s="72"/>
     </row>
     <row r="95" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="53"/>
-      <c r="C95" s="39"/>
-      <c r="D95" s="76" t="s">
-        <v>88</v>
+      <c r="B95" s="52"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="85" t="s">
+        <v>101</v>
       </c>
       <c r="E95" s="2"/>
-      <c r="F95" s="35"/>
-      <c r="G95" s="58"/>
-      <c r="H95" s="58">
+      <c r="F95" s="34"/>
+      <c r="G95" s="57"/>
+      <c r="H95" s="57">
         <f>E95*G95</f>
         <v>0</v>
       </c>
-      <c r="I95" s="66"/>
-      <c r="J95" s="66"/>
-      <c r="K95" s="66"/>
-      <c r="L95" s="66"/>
-      <c r="M95" s="66"/>
+      <c r="I95" s="72"/>
+      <c r="J95" s="72"/>
+      <c r="K95" s="72"/>
+      <c r="L95" s="72"/>
+      <c r="M95" s="72"/>
     </row>
     <row r="96" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="53"/>
-      <c r="C96" s="39"/>
-      <c r="D96" s="122" t="s">
-        <v>197</v>
+      <c r="B96" s="52"/>
+      <c r="C96" s="38"/>
+      <c r="D96" s="38" t="s">
+        <v>102</v>
       </c>
       <c r="E96" s="2"/>
-      <c r="F96" s="35"/>
+      <c r="F96" s="34"/>
       <c r="G96" s="2"/>
-      <c r="H96" s="126">
-        <v>7895</v>
-      </c>
-      <c r="I96" s="66"/>
-      <c r="J96" s="66"/>
-      <c r="K96" s="66"/>
-      <c r="L96" s="66"/>
-      <c r="M96" s="66"/>
+      <c r="H96" s="150">
+        <v>9395</v>
+      </c>
+      <c r="I96" s="78" t="s">
+        <v>103</v>
+      </c>
+      <c r="J96" s="78"/>
+      <c r="K96" s="78"/>
+      <c r="L96" s="78"/>
+      <c r="M96" s="72"/>
     </row>
     <row r="97" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B97" s="53"/>
-      <c r="C97" s="39"/>
-      <c r="D97" s="39"/>
+      <c r="B97" s="52"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="38"/>
       <c r="E97" s="2"/>
-      <c r="F97" s="35"/>
+      <c r="F97" s="34"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="58"/>
+      <c r="H97" s="57"/>
     </row>
     <row r="98" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="48"/>
-      <c r="B98" s="138" t="s">
-        <v>89</v>
-      </c>
-      <c r="C98" s="136"/>
-      <c r="D98" s="137"/>
-      <c r="E98" s="49"/>
-      <c r="F98" s="50"/>
-      <c r="G98" s="51"/>
-      <c r="H98" s="49">
+      <c r="A98" s="47"/>
+      <c r="B98" s="139" t="s">
+        <v>104</v>
+      </c>
+      <c r="C98" s="137"/>
+      <c r="D98" s="138"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="49"/>
+      <c r="G98" s="50"/>
+      <c r="H98" s="48">
         <f>SUM(H99:H108)</f>
-        <v>124365</v>
-      </c>
-      <c r="I98" s="52"/>
-      <c r="J98" s="48"/>
-      <c r="K98" s="48"/>
-      <c r="L98" s="48"/>
-      <c r="M98" s="48"/>
-      <c r="N98" s="48"/>
-      <c r="O98" s="48"/>
-      <c r="P98" s="48"/>
-      <c r="Q98" s="48"/>
-      <c r="R98" s="48"/>
-      <c r="S98" s="48"/>
-      <c r="T98" s="48"/>
-      <c r="U98" s="48"/>
-      <c r="V98" s="48"/>
-      <c r="W98" s="48"/>
-      <c r="X98" s="48"/>
-      <c r="Y98" s="48"/>
-      <c r="Z98" s="48"/>
+        <v>136665</v>
+      </c>
+      <c r="I98" s="51"/>
+      <c r="J98" s="47"/>
+      <c r="K98" s="47"/>
+      <c r="L98" s="47"/>
+      <c r="M98" s="47"/>
+      <c r="N98" s="47"/>
+      <c r="O98" s="47"/>
+      <c r="P98" s="47"/>
+      <c r="Q98" s="47"/>
+      <c r="R98" s="47"/>
+      <c r="S98" s="47"/>
+      <c r="T98" s="47"/>
+      <c r="U98" s="47"/>
+      <c r="V98" s="47"/>
+      <c r="W98" s="47"/>
+      <c r="X98" s="47"/>
+      <c r="Y98" s="47"/>
+      <c r="Z98" s="47"/>
     </row>
     <row r="99" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="53"/>
-      <c r="C99" s="39"/>
-      <c r="D99" s="32" t="s">
-        <v>90</v>
+      <c r="B99" s="52"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="31" t="s">
+        <v>105</v>
       </c>
       <c r="E99" s="2"/>
-      <c r="F99" s="35"/>
-      <c r="G99" s="77"/>
-      <c r="H99" s="126">
-        <v>68465</v>
-      </c>
-      <c r="I99" s="145" t="s">
-        <v>204</v>
-      </c>
-      <c r="J99" s="145"/>
-      <c r="K99" s="146"/>
-      <c r="L99" s="146"/>
-      <c r="M99" s="146"/>
-      <c r="N99" s="145"/>
-      <c r="O99" s="121"/>
-      <c r="P99" s="121"/>
+      <c r="F99" s="34"/>
+      <c r="G99" s="86"/>
+      <c r="H99" s="150">
+        <v>75015</v>
+      </c>
+      <c r="I99" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="J99" s="78"/>
+      <c r="K99" s="78"/>
+      <c r="L99" s="78"/>
+      <c r="M99" s="78"/>
+      <c r="N99" s="78"/>
+      <c r="O99" s="58"/>
+      <c r="P99" s="58"/>
     </row>
     <row r="100" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="53"/>
-      <c r="C100" s="39"/>
-      <c r="D100" s="32" t="s">
-        <v>91</v>
+      <c r="B100" s="52"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="31" t="s">
+        <v>107</v>
       </c>
       <c r="E100" s="2"/>
-      <c r="F100" s="35"/>
-      <c r="G100" s="77"/>
-      <c r="H100" s="58">
-        <v>31380</v>
-      </c>
-      <c r="I100" s="66"/>
-      <c r="J100" s="66"/>
-      <c r="K100" s="66"/>
-      <c r="L100" s="66"/>
-      <c r="M100" s="66"/>
-      <c r="N100" s="66"/>
+      <c r="F100" s="34"/>
+      <c r="G100" s="86"/>
+      <c r="H100" s="151">
+        <v>35755</v>
+      </c>
+      <c r="I100" s="148" t="s">
+        <v>216</v>
+      </c>
+      <c r="J100" s="148"/>
+      <c r="K100" s="148"/>
+      <c r="L100" s="148"/>
+      <c r="M100" s="148"/>
+      <c r="N100" s="148"/>
+      <c r="O100" s="149"/>
     </row>
     <row r="101" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="53"/>
-      <c r="C101" s="39"/>
-      <c r="D101" s="32" t="s">
-        <v>92</v>
+      <c r="B101" s="52"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="31" t="s">
+        <v>108</v>
       </c>
       <c r="E101" s="2"/>
-      <c r="F101" s="35"/>
-      <c r="G101" s="77"/>
-      <c r="H101" s="56">
-        <v>4200</v>
-      </c>
-      <c r="I101" s="66"/>
-      <c r="J101" s="66"/>
-      <c r="K101" s="66"/>
-      <c r="L101" s="66"/>
-      <c r="M101" s="66"/>
-      <c r="N101" s="66"/>
+      <c r="F101" s="34"/>
+      <c r="G101" s="86"/>
+      <c r="H101" s="150">
+        <v>5575</v>
+      </c>
+      <c r="I101" s="148" t="s">
+        <v>215</v>
+      </c>
+      <c r="J101" s="148"/>
+      <c r="K101" s="148"/>
+      <c r="L101" s="72"/>
+      <c r="M101" s="72"/>
+      <c r="N101" s="72"/>
     </row>
     <row r="102" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="53"/>
-      <c r="C102" s="39"/>
-      <c r="D102" s="73" t="s">
-        <v>93</v>
+      <c r="B102" s="52"/>
+      <c r="C102" s="38"/>
+      <c r="D102" s="82" t="s">
+        <v>109</v>
       </c>
       <c r="E102" s="2"/>
-      <c r="F102" s="35"/>
-      <c r="G102" s="77"/>
-      <c r="H102" s="56">
+      <c r="F102" s="34"/>
+      <c r="G102" s="86"/>
+      <c r="H102" s="55">
         <v>9225</v>
       </c>
-      <c r="I102" s="66"/>
-      <c r="J102" s="66"/>
-      <c r="K102" s="66"/>
-      <c r="L102" s="66"/>
-      <c r="M102" s="66"/>
-      <c r="N102" s="66"/>
+      <c r="I102" s="153" t="s">
+        <v>217</v>
+      </c>
+      <c r="J102" s="87"/>
+      <c r="K102" s="87"/>
+      <c r="L102" s="154"/>
+      <c r="M102" s="72"/>
+      <c r="N102" s="72"/>
     </row>
     <row r="103" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="53"/>
-      <c r="C103" s="79"/>
-      <c r="D103" s="80" t="s">
-        <v>94</v>
+      <c r="B103" s="52"/>
+      <c r="C103" s="88"/>
+      <c r="D103" s="89" t="s">
+        <v>110</v>
       </c>
       <c r="E103" s="2"/>
-      <c r="F103" s="35"/>
-      <c r="G103" s="77"/>
-      <c r="H103" s="58">
+      <c r="F103" s="34"/>
+      <c r="G103" s="86"/>
+      <c r="H103" s="57">
         <v>1325</v>
       </c>
-      <c r="I103" s="66"/>
-      <c r="J103" s="66"/>
-      <c r="K103" s="66"/>
-      <c r="L103" s="66"/>
-      <c r="M103" s="66"/>
-      <c r="N103" s="66"/>
+      <c r="I103" s="72"/>
+      <c r="J103" s="72"/>
+      <c r="K103" s="72"/>
+      <c r="L103" s="72"/>
+      <c r="M103" s="72"/>
+      <c r="N103" s="72"/>
     </row>
     <row r="104" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="53"/>
-      <c r="C104" s="39"/>
-      <c r="D104" s="81" t="s">
-        <v>95</v>
+      <c r="B104" s="52"/>
+      <c r="C104" s="38"/>
+      <c r="D104" s="90" t="s">
+        <v>111</v>
       </c>
       <c r="E104" s="2"/>
-      <c r="F104" s="35"/>
-      <c r="G104" s="77"/>
-      <c r="H104" s="58">
+      <c r="F104" s="34"/>
+      <c r="G104" s="86"/>
+      <c r="H104" s="57">
         <v>9770</v>
       </c>
-      <c r="I104" s="66"/>
-      <c r="J104" s="66"/>
-      <c r="K104" s="66"/>
-      <c r="L104" s="66"/>
-      <c r="M104" s="66"/>
-      <c r="N104" s="66"/>
-      <c r="O104" s="66"/>
-      <c r="P104" s="66"/>
-      <c r="Q104" s="66"/>
+      <c r="I104" s="72"/>
+      <c r="J104" s="72"/>
+      <c r="K104" s="72"/>
+      <c r="L104" s="72"/>
+      <c r="M104" s="72"/>
+      <c r="N104" s="72"/>
+      <c r="O104" s="72"/>
+      <c r="P104" s="72"/>
+      <c r="Q104" s="72"/>
     </row>
     <row r="105" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="53"/>
-      <c r="C105" s="39"/>
-      <c r="D105" s="32" t="s">
-        <v>96</v>
+      <c r="B105" s="52"/>
+      <c r="C105" s="38"/>
+      <c r="D105" s="31" t="s">
+        <v>112</v>
       </c>
       <c r="E105" s="2"/>
-      <c r="F105" s="35"/>
-      <c r="G105" s="77"/>
-      <c r="H105" s="58">
+      <c r="F105" s="34"/>
+      <c r="G105" s="86"/>
+      <c r="H105" s="57">
         <f t="shared" ref="H105:H106" si="5">E105*G105</f>
         <v>0</v>
       </c>
-      <c r="I105" s="66"/>
-      <c r="J105" s="66"/>
-      <c r="K105" s="66"/>
-      <c r="L105" s="66"/>
-      <c r="M105" s="66"/>
-      <c r="N105" s="66"/>
+      <c r="I105" s="72"/>
+      <c r="J105" s="72"/>
+      <c r="K105" s="72"/>
+      <c r="L105" s="72"/>
+      <c r="M105" s="72"/>
+      <c r="N105" s="72"/>
     </row>
     <row r="106" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="53"/>
-      <c r="C106" s="39"/>
-      <c r="D106" s="82" t="s">
-        <v>97</v>
+      <c r="B106" s="52"/>
+      <c r="C106" s="38"/>
+      <c r="D106" s="91" t="s">
+        <v>113</v>
       </c>
       <c r="E106" s="2"/>
-      <c r="F106" s="35"/>
-      <c r="G106" s="77"/>
-      <c r="H106" s="58">
+      <c r="F106" s="34"/>
+      <c r="G106" s="86"/>
+      <c r="H106" s="57">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I106" s="66"/>
-      <c r="J106" s="66"/>
-      <c r="K106" s="66"/>
-      <c r="L106" s="66"/>
-      <c r="M106" s="66"/>
-      <c r="N106" s="66"/>
+      <c r="I106" s="72"/>
+      <c r="J106" s="72"/>
+      <c r="K106" s="72"/>
+      <c r="L106" s="72"/>
+      <c r="M106" s="72"/>
+      <c r="N106" s="72"/>
     </row>
     <row r="107" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="53"/>
-      <c r="C107" s="39"/>
-      <c r="D107" s="32" t="s">
-        <v>98</v>
+      <c r="B107" s="52"/>
+      <c r="C107" s="38"/>
+      <c r="D107" s="31" t="s">
+        <v>114</v>
       </c>
       <c r="E107" s="2"/>
-      <c r="F107" s="35"/>
-      <c r="G107" s="77"/>
-      <c r="H107" s="58">
+      <c r="F107" s="34"/>
+      <c r="G107" s="86"/>
+      <c r="H107" s="57">
         <v>0</v>
       </c>
-      <c r="I107" s="66"/>
-      <c r="J107" s="66"/>
-      <c r="K107" s="66"/>
-      <c r="L107" s="66"/>
-      <c r="M107" s="66"/>
-      <c r="N107" s="66"/>
+      <c r="I107" s="72"/>
+      <c r="J107" s="72"/>
+      <c r="K107" s="72"/>
+      <c r="L107" s="72"/>
+      <c r="M107" s="72"/>
+      <c r="N107" s="72"/>
     </row>
     <row r="108" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="53"/>
-      <c r="C108" s="39"/>
-      <c r="D108" s="39" t="s">
-        <v>63</v>
+      <c r="B108" s="52"/>
+      <c r="C108" s="38"/>
+      <c r="D108" s="38" t="s">
+        <v>74</v>
       </c>
       <c r="E108" s="2"/>
-      <c r="F108" s="35"/>
-      <c r="G108" s="77"/>
-      <c r="H108" s="58">
+      <c r="F108" s="34"/>
+      <c r="G108" s="86"/>
+      <c r="H108" s="57">
         <f>E108*G108</f>
         <v>0</v>
       </c>
-      <c r="I108" s="66"/>
-      <c r="J108" s="66"/>
-      <c r="K108" s="66"/>
-      <c r="L108" s="66"/>
-      <c r="M108" s="66"/>
-      <c r="N108" s="66"/>
+      <c r="I108" s="72"/>
+      <c r="J108" s="72"/>
+      <c r="K108" s="72"/>
+      <c r="L108" s="72"/>
+      <c r="M108" s="72"/>
+      <c r="N108" s="72"/>
     </row>
     <row r="109" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B109" s="53"/>
-      <c r="C109" s="39"/>
-      <c r="D109" s="39"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="38"/>
+      <c r="D109" s="38"/>
       <c r="E109" s="2"/>
-      <c r="F109" s="35"/>
+      <c r="F109" s="34"/>
       <c r="G109" s="2"/>
-      <c r="H109" s="58"/>
+      <c r="H109" s="57"/>
     </row>
     <row r="110" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="48"/>
-      <c r="B110" s="138" t="s">
-        <v>99</v>
-      </c>
-      <c r="C110" s="136"/>
-      <c r="D110" s="137"/>
-      <c r="E110" s="49"/>
-      <c r="F110" s="50"/>
-      <c r="G110" s="51"/>
-      <c r="H110" s="49">
+      <c r="A110" s="47"/>
+      <c r="B110" s="139" t="s">
+        <v>115</v>
+      </c>
+      <c r="C110" s="137"/>
+      <c r="D110" s="138"/>
+      <c r="E110" s="48"/>
+      <c r="F110" s="49"/>
+      <c r="G110" s="50"/>
+      <c r="H110" s="48">
         <f>SUM(H111:H123)</f>
         <v>16912</v>
       </c>
-      <c r="I110" s="52"/>
-      <c r="J110" s="48"/>
-      <c r="K110" s="48"/>
-      <c r="L110" s="48"/>
-      <c r="M110" s="48"/>
-      <c r="N110" s="48"/>
-      <c r="O110" s="48"/>
-      <c r="P110" s="48"/>
-      <c r="Q110" s="48"/>
-      <c r="R110" s="48"/>
-      <c r="S110" s="48"/>
-      <c r="T110" s="48"/>
-      <c r="U110" s="48"/>
-      <c r="V110" s="48"/>
-      <c r="W110" s="48"/>
-      <c r="X110" s="48"/>
-      <c r="Y110" s="48"/>
-      <c r="Z110" s="48"/>
+      <c r="I110" s="51"/>
+      <c r="J110" s="47"/>
+      <c r="K110" s="47"/>
+      <c r="L110" s="47"/>
+      <c r="M110" s="47"/>
+      <c r="N110" s="47"/>
+      <c r="O110" s="47"/>
+      <c r="P110" s="47"/>
+      <c r="Q110" s="47"/>
+      <c r="R110" s="47"/>
+      <c r="S110" s="47"/>
+      <c r="T110" s="47"/>
+      <c r="U110" s="47"/>
+      <c r="V110" s="47"/>
+      <c r="W110" s="47"/>
+      <c r="X110" s="47"/>
+      <c r="Y110" s="47"/>
+      <c r="Z110" s="47"/>
     </row>
     <row r="111" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="52"/>
-      <c r="B111" s="32"/>
-      <c r="C111" s="83"/>
-      <c r="D111" s="32" t="s">
-        <v>100</v>
+      <c r="A111" s="51"/>
+      <c r="B111" s="31"/>
+      <c r="C111" s="92"/>
+      <c r="D111" s="31" t="s">
+        <v>116</v>
       </c>
       <c r="E111" s="2"/>
-      <c r="F111" s="35"/>
-      <c r="G111" s="58"/>
-      <c r="H111" s="56">
+      <c r="F111" s="34"/>
+      <c r="G111" s="57"/>
+      <c r="H111" s="55">
         <v>3500</v>
       </c>
-      <c r="I111" s="84"/>
-      <c r="J111" s="84"/>
-      <c r="K111" s="52"/>
-      <c r="L111" s="52"/>
-      <c r="M111" s="52"/>
-      <c r="N111" s="52"/>
-      <c r="O111" s="52"/>
-      <c r="P111" s="52"/>
-      <c r="Q111" s="52"/>
-      <c r="R111" s="52"/>
-      <c r="S111" s="52"/>
-      <c r="T111" s="52"/>
-      <c r="U111" s="52"/>
-      <c r="V111" s="52"/>
-      <c r="W111" s="52"/>
-      <c r="X111" s="52"/>
-      <c r="Y111" s="52"/>
-      <c r="Z111" s="52"/>
+      <c r="I111" s="93"/>
+      <c r="J111" s="93"/>
+      <c r="K111" s="51"/>
+      <c r="L111" s="51"/>
+      <c r="M111" s="51"/>
+      <c r="N111" s="51"/>
+      <c r="O111" s="51"/>
+      <c r="P111" s="51"/>
+      <c r="Q111" s="51"/>
+      <c r="R111" s="51"/>
+      <c r="S111" s="51"/>
+      <c r="T111" s="51"/>
+      <c r="U111" s="51"/>
+      <c r="V111" s="51"/>
+      <c r="W111" s="51"/>
+      <c r="X111" s="51"/>
+      <c r="Y111" s="51"/>
+      <c r="Z111" s="51"/>
     </row>
     <row r="112" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="52"/>
-      <c r="B112" s="32"/>
-      <c r="C112" s="83"/>
-      <c r="D112" s="32" t="s">
-        <v>101</v>
+      <c r="A112" s="51"/>
+      <c r="B112" s="31"/>
+      <c r="C112" s="92"/>
+      <c r="D112" s="31" t="s">
+        <v>117</v>
       </c>
       <c r="E112" s="2"/>
-      <c r="F112" s="35"/>
-      <c r="G112" s="58"/>
-      <c r="H112" s="56">
+      <c r="F112" s="34"/>
+      <c r="G112" s="57"/>
+      <c r="H112" s="55">
         <v>11250</v>
       </c>
-      <c r="I112" s="84"/>
-      <c r="J112" s="84"/>
-      <c r="K112" s="52"/>
-      <c r="L112" s="52"/>
-      <c r="M112" s="52"/>
-      <c r="N112" s="52"/>
-      <c r="O112" s="52"/>
-      <c r="P112" s="52"/>
-      <c r="Q112" s="52"/>
-      <c r="R112" s="52"/>
-      <c r="S112" s="52"/>
-      <c r="T112" s="52"/>
-      <c r="U112" s="52"/>
-      <c r="V112" s="52"/>
-      <c r="W112" s="52"/>
-      <c r="X112" s="52"/>
-      <c r="Y112" s="52"/>
-      <c r="Z112" s="52"/>
+      <c r="I112" s="93"/>
+      <c r="J112" s="93"/>
+      <c r="K112" s="51"/>
+      <c r="L112" s="51"/>
+      <c r="M112" s="51"/>
+      <c r="N112" s="51"/>
+      <c r="O112" s="51"/>
+      <c r="P112" s="51"/>
+      <c r="Q112" s="51"/>
+      <c r="R112" s="51"/>
+      <c r="S112" s="51"/>
+      <c r="T112" s="51"/>
+      <c r="U112" s="51"/>
+      <c r="V112" s="51"/>
+      <c r="W112" s="51"/>
+      <c r="X112" s="51"/>
+      <c r="Y112" s="51"/>
+      <c r="Z112" s="51"/>
     </row>
     <row r="113" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="32"/>
-      <c r="C113" s="39"/>
-      <c r="D113" s="32" t="s">
-        <v>102</v>
+      <c r="B113" s="31"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="31" t="s">
+        <v>118</v>
       </c>
       <c r="E113" s="2"/>
-      <c r="F113" s="35"/>
-      <c r="G113" s="58"/>
-      <c r="H113" s="58">
+      <c r="F113" s="34"/>
+      <c r="G113" s="57"/>
+      <c r="H113" s="57">
         <f t="shared" ref="H113:H114" si="6">E113*G113</f>
         <v>0</v>
       </c>
-      <c r="I113" s="84"/>
-      <c r="J113" s="84"/>
+      <c r="I113" s="93"/>
+      <c r="J113" s="93"/>
     </row>
     <row r="114" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B114" s="32"/>
-      <c r="C114" s="39"/>
-      <c r="D114" s="32" t="s">
-        <v>103</v>
+      <c r="B114" s="31"/>
+      <c r="C114" s="38"/>
+      <c r="D114" s="31" t="s">
+        <v>119</v>
       </c>
       <c r="E114" s="2"/>
-      <c r="F114" s="35"/>
-      <c r="G114" s="58"/>
-      <c r="H114" s="58">
+      <c r="F114" s="34"/>
+      <c r="G114" s="57"/>
+      <c r="H114" s="57">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I114" s="84"/>
-      <c r="J114" s="84"/>
+      <c r="I114" s="93"/>
+      <c r="J114" s="93"/>
     </row>
     <row r="115" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B115" s="32"/>
-      <c r="C115" s="39"/>
-      <c r="D115" s="32" t="s">
-        <v>104</v>
+      <c r="B115" s="31"/>
+      <c r="C115" s="38"/>
+      <c r="D115" s="31" t="s">
+        <v>120</v>
       </c>
       <c r="E115" s="2"/>
-      <c r="F115" s="35"/>
-      <c r="G115" s="58"/>
-      <c r="H115" s="56">
+      <c r="F115" s="34"/>
+      <c r="G115" s="57"/>
+      <c r="H115" s="55">
         <v>1875</v>
       </c>
-      <c r="I115" s="84"/>
-      <c r="J115" s="84"/>
+      <c r="I115" s="93"/>
+      <c r="J115" s="93"/>
     </row>
     <row r="116" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B116" s="32"/>
-      <c r="C116" s="39"/>
-      <c r="D116" s="32" t="s">
-        <v>105</v>
+      <c r="B116" s="31"/>
+      <c r="C116" s="38"/>
+      <c r="D116" s="31" t="s">
+        <v>121</v>
       </c>
       <c r="E116" s="2"/>
-      <c r="F116" s="35"/>
-      <c r="G116" s="58"/>
-      <c r="H116" s="56">
+      <c r="F116" s="34"/>
+      <c r="G116" s="57"/>
+      <c r="H116" s="55">
         <v>287</v>
       </c>
-      <c r="I116" s="84"/>
-      <c r="J116" s="84"/>
+      <c r="I116" s="93"/>
+      <c r="J116" s="93"/>
     </row>
     <row r="117" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="32"/>
-      <c r="C117" s="39"/>
-      <c r="D117" s="33" t="s">
-        <v>106</v>
+      <c r="B117" s="31"/>
+      <c r="C117" s="38"/>
+      <c r="D117" s="32" t="s">
+        <v>122</v>
       </c>
       <c r="E117" s="2"/>
-      <c r="F117" s="35"/>
-      <c r="G117" s="58"/>
-      <c r="H117" s="58">
+      <c r="F117" s="34"/>
+      <c r="G117" s="57"/>
+      <c r="H117" s="57">
         <f t="shared" ref="H117:H123" si="7">E117*G117</f>
         <v>0</v>
       </c>
-      <c r="I117" s="84"/>
-      <c r="J117" s="84"/>
+      <c r="I117" s="93"/>
+      <c r="J117" s="93"/>
     </row>
     <row r="118" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B118" s="32"/>
-      <c r="C118" s="39"/>
-      <c r="D118" s="85" t="s">
-        <v>107</v>
+      <c r="B118" s="31"/>
+      <c r="C118" s="38"/>
+      <c r="D118" s="94" t="s">
+        <v>123</v>
       </c>
       <c r="E118" s="2"/>
-      <c r="F118" s="35"/>
-      <c r="G118" s="58"/>
-      <c r="H118" s="58">
+      <c r="F118" s="34"/>
+      <c r="G118" s="57"/>
+      <c r="H118" s="57">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I118" s="84"/>
-      <c r="J118" s="84"/>
+      <c r="I118" s="93"/>
+      <c r="J118" s="93"/>
     </row>
     <row r="119" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B119" s="32"/>
-      <c r="C119" s="39"/>
-      <c r="D119" s="85" t="s">
-        <v>108</v>
+      <c r="B119" s="31"/>
+      <c r="C119" s="38"/>
+      <c r="D119" s="94" t="s">
+        <v>124</v>
       </c>
       <c r="E119" s="2"/>
-      <c r="F119" s="35"/>
-      <c r="G119" s="58"/>
-      <c r="H119" s="58">
+      <c r="F119" s="34"/>
+      <c r="G119" s="57"/>
+      <c r="H119" s="57">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I119" s="84"/>
-      <c r="J119" s="84"/>
+      <c r="I119" s="93"/>
+      <c r="J119" s="93"/>
     </row>
     <row r="120" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="32"/>
-      <c r="C120" s="39"/>
-      <c r="D120" s="85" t="s">
-        <v>109</v>
+      <c r="B120" s="31"/>
+      <c r="C120" s="38"/>
+      <c r="D120" s="94" t="s">
+        <v>125</v>
       </c>
       <c r="E120" s="2"/>
-      <c r="F120" s="35"/>
-      <c r="G120" s="58"/>
-      <c r="H120" s="58">
+      <c r="F120" s="34"/>
+      <c r="G120" s="57"/>
+      <c r="H120" s="57">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I120" s="84"/>
-      <c r="J120" s="84"/>
+      <c r="I120" s="93"/>
+      <c r="J120" s="93"/>
     </row>
     <row r="121" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="32"/>
-      <c r="C121" s="39"/>
-      <c r="D121" s="85" t="s">
-        <v>110</v>
+      <c r="B121" s="31"/>
+      <c r="C121" s="38"/>
+      <c r="D121" s="94" t="s">
+        <v>126</v>
       </c>
       <c r="E121" s="2"/>
-      <c r="F121" s="35"/>
-      <c r="G121" s="58"/>
-      <c r="H121" s="58">
+      <c r="F121" s="34"/>
+      <c r="G121" s="57"/>
+      <c r="H121" s="57">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I121" s="84"/>
-      <c r="J121" s="84"/>
+      <c r="I121" s="93"/>
+      <c r="J121" s="93"/>
     </row>
     <row r="122" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="32"/>
-      <c r="C122" s="39"/>
-      <c r="D122" s="85" t="s">
-        <v>111</v>
+      <c r="B122" s="31"/>
+      <c r="C122" s="38"/>
+      <c r="D122" s="94" t="s">
+        <v>127</v>
       </c>
       <c r="E122" s="2"/>
-      <c r="F122" s="35"/>
-      <c r="G122" s="58"/>
-      <c r="H122" s="58">
+      <c r="F122" s="34"/>
+      <c r="G122" s="57"/>
+      <c r="H122" s="57">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I122" s="84"/>
-      <c r="J122" s="84"/>
+      <c r="I122" s="93"/>
+      <c r="J122" s="93"/>
     </row>
     <row r="123" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="32"/>
-      <c r="C123" s="39"/>
-      <c r="D123" s="32"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="38"/>
+      <c r="D123" s="31"/>
       <c r="E123" s="2"/>
-      <c r="F123" s="35"/>
-      <c r="G123" s="58"/>
-      <c r="H123" s="58">
+      <c r="F123" s="34"/>
+      <c r="G123" s="57"/>
+      <c r="H123" s="57">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I123" s="84"/>
-      <c r="J123" s="84"/>
+      <c r="I123" s="93"/>
+      <c r="J123" s="93"/>
     </row>
     <row r="124" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="32"/>
-      <c r="C124" s="39"/>
-      <c r="D124" s="32"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="38"/>
+      <c r="D124" s="31"/>
       <c r="E124" s="2"/>
-      <c r="F124" s="35"/>
-      <c r="G124" s="58"/>
-      <c r="H124" s="58"/>
-      <c r="I124" s="84"/>
-      <c r="J124" s="84"/>
+      <c r="F124" s="34"/>
+      <c r="G124" s="57"/>
+      <c r="H124" s="57"/>
+      <c r="I124" s="93"/>
+      <c r="J124" s="93"/>
     </row>
     <row r="125" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="48"/>
-      <c r="B125" s="138" t="s">
-        <v>112</v>
-      </c>
-      <c r="C125" s="136"/>
-      <c r="D125" s="137"/>
-      <c r="E125" s="49"/>
-      <c r="F125" s="50"/>
-      <c r="G125" s="51"/>
-      <c r="H125" s="49">
+      <c r="A125" s="47"/>
+      <c r="B125" s="139" t="s">
+        <v>128</v>
+      </c>
+      <c r="C125" s="137"/>
+      <c r="D125" s="138"/>
+      <c r="E125" s="48"/>
+      <c r="F125" s="49"/>
+      <c r="G125" s="50"/>
+      <c r="H125" s="48">
         <f>SUM(H127:H131)</f>
         <v>2335</v>
       </c>
-      <c r="I125" s="52"/>
-      <c r="J125" s="48"/>
-      <c r="K125" s="48"/>
-      <c r="L125" s="48"/>
-      <c r="M125" s="48"/>
-      <c r="N125" s="48"/>
-      <c r="O125" s="48"/>
-      <c r="P125" s="48"/>
-      <c r="Q125" s="48"/>
-      <c r="R125" s="48"/>
-      <c r="S125" s="48"/>
-      <c r="T125" s="48"/>
-      <c r="U125" s="48"/>
-      <c r="V125" s="48"/>
-      <c r="W125" s="48"/>
-      <c r="X125" s="48"/>
-      <c r="Y125" s="48"/>
-      <c r="Z125" s="48"/>
+      <c r="I125" s="51"/>
+      <c r="J125" s="47"/>
+      <c r="K125" s="47"/>
+      <c r="L125" s="47"/>
+      <c r="M125" s="47"/>
+      <c r="N125" s="47"/>
+      <c r="O125" s="47"/>
+      <c r="P125" s="47"/>
+      <c r="Q125" s="47"/>
+      <c r="R125" s="47"/>
+      <c r="S125" s="47"/>
+      <c r="T125" s="47"/>
+      <c r="U125" s="47"/>
+      <c r="V125" s="47"/>
+      <c r="W125" s="47"/>
+      <c r="X125" s="47"/>
+      <c r="Y125" s="47"/>
+      <c r="Z125" s="47"/>
     </row>
     <row r="126" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="32"/>
-      <c r="C126" s="39"/>
-      <c r="D126" s="33" t="s">
-        <v>113</v>
+      <c r="B126" s="31"/>
+      <c r="C126" s="38"/>
+      <c r="D126" s="32" t="s">
+        <v>129</v>
       </c>
       <c r="E126" s="2"/>
-      <c r="F126" s="35"/>
-      <c r="G126" s="77"/>
-      <c r="H126" s="58"/>
+      <c r="F126" s="34"/>
+      <c r="G126" s="86"/>
+      <c r="H126" s="57"/>
     </row>
     <row r="127" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="32"/>
-      <c r="C127" s="39"/>
-      <c r="D127" s="85" t="s">
-        <v>114</v>
+      <c r="B127" s="31"/>
+      <c r="C127" s="38"/>
+      <c r="D127" s="94" t="s">
+        <v>130</v>
       </c>
       <c r="E127" s="2"/>
-      <c r="F127" s="35"/>
-      <c r="G127" s="58"/>
-      <c r="H127" s="56">
+      <c r="F127" s="34"/>
+      <c r="G127" s="57"/>
+      <c r="H127" s="55">
         <v>1600</v>
       </c>
     </row>
     <row r="128" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B128" s="32"/>
-      <c r="C128" s="39"/>
-      <c r="D128" s="85" t="s">
-        <v>115</v>
+      <c r="B128" s="31"/>
+      <c r="C128" s="38"/>
+      <c r="D128" s="94" t="s">
+        <v>131</v>
       </c>
       <c r="E128" s="2"/>
-      <c r="F128" s="35"/>
-      <c r="G128" s="58"/>
-      <c r="H128" s="56">
+      <c r="F128" s="34"/>
+      <c r="G128" s="57"/>
+      <c r="H128" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B129" s="32"/>
-      <c r="C129" s="39"/>
-      <c r="D129" s="85" t="s">
-        <v>116</v>
+      <c r="B129" s="31"/>
+      <c r="C129" s="38"/>
+      <c r="D129" s="94" t="s">
+        <v>132</v>
       </c>
       <c r="E129" s="2"/>
-      <c r="F129" s="35"/>
-      <c r="G129" s="58"/>
-      <c r="H129" s="56">
+      <c r="F129" s="34"/>
+      <c r="G129" s="57"/>
+      <c r="H129" s="55">
         <v>360</v>
       </c>
     </row>
     <row r="130" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B130" s="32"/>
-      <c r="C130" s="39"/>
-      <c r="D130" s="85" t="s">
-        <v>117</v>
+      <c r="B130" s="31"/>
+      <c r="C130" s="38"/>
+      <c r="D130" s="94" t="s">
+        <v>133</v>
       </c>
       <c r="E130" s="2"/>
-      <c r="F130" s="35"/>
-      <c r="G130" s="58"/>
-      <c r="H130" s="56">
+      <c r="F130" s="34"/>
+      <c r="G130" s="57"/>
+      <c r="H130" s="55">
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B131" s="32"/>
-      <c r="C131" s="39"/>
-      <c r="D131" s="32" t="s">
-        <v>118</v>
+      <c r="B131" s="31"/>
+      <c r="C131" s="38"/>
+      <c r="D131" s="31" t="s">
+        <v>134</v>
       </c>
       <c r="E131" s="2"/>
-      <c r="F131" s="35"/>
-      <c r="G131" s="58"/>
-      <c r="H131" s="56">
+      <c r="F131" s="34"/>
+      <c r="G131" s="57"/>
+      <c r="H131" s="55">
         <v>375</v>
       </c>
     </row>
     <row r="132" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B132" s="32"/>
-      <c r="C132" s="39"/>
-      <c r="D132" s="32"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="38"/>
+      <c r="D132" s="31"/>
       <c r="E132" s="2"/>
-      <c r="F132" s="35"/>
+      <c r="F132" s="34"/>
       <c r="G132" s="2"/>
-      <c r="H132" s="58"/>
+      <c r="H132" s="57"/>
     </row>
     <row r="133" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="48"/>
-      <c r="B133" s="138" t="s">
-        <v>119</v>
-      </c>
-      <c r="C133" s="136"/>
-      <c r="D133" s="137"/>
-      <c r="E133" s="49"/>
-      <c r="F133" s="50"/>
-      <c r="G133" s="51"/>
-      <c r="H133" s="49">
+      <c r="A133" s="47"/>
+      <c r="B133" s="139" t="s">
+        <v>135</v>
+      </c>
+      <c r="C133" s="137"/>
+      <c r="D133" s="138"/>
+      <c r="E133" s="48"/>
+      <c r="F133" s="49"/>
+      <c r="G133" s="50"/>
+      <c r="H133" s="48">
         <f>SUM(H134)</f>
         <v>0</v>
       </c>
-      <c r="I133" s="52"/>
-      <c r="J133" s="48"/>
-      <c r="K133" s="48"/>
-      <c r="L133" s="48"/>
-      <c r="M133" s="48"/>
-      <c r="N133" s="48"/>
-      <c r="O133" s="48"/>
-      <c r="P133" s="48"/>
-      <c r="Q133" s="48"/>
-      <c r="R133" s="48"/>
-      <c r="S133" s="48"/>
-      <c r="T133" s="48"/>
-      <c r="U133" s="48"/>
-      <c r="V133" s="48"/>
-      <c r="W133" s="48"/>
-      <c r="X133" s="48"/>
-      <c r="Y133" s="48"/>
-      <c r="Z133" s="48"/>
+      <c r="I133" s="51"/>
+      <c r="J133" s="47"/>
+      <c r="K133" s="47"/>
+      <c r="L133" s="47"/>
+      <c r="M133" s="47"/>
+      <c r="N133" s="47"/>
+      <c r="O133" s="47"/>
+      <c r="P133" s="47"/>
+      <c r="Q133" s="47"/>
+      <c r="R133" s="47"/>
+      <c r="S133" s="47"/>
+      <c r="T133" s="47"/>
+      <c r="U133" s="47"/>
+      <c r="V133" s="47"/>
+      <c r="W133" s="47"/>
+      <c r="X133" s="47"/>
+      <c r="Y133" s="47"/>
+      <c r="Z133" s="47"/>
     </row>
     <row r="134" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="32"/>
-      <c r="C134" s="39"/>
-      <c r="D134" s="32" t="s">
-        <v>120</v>
+      <c r="B134" s="31"/>
+      <c r="C134" s="38"/>
+      <c r="D134" s="31" t="s">
+        <v>136</v>
       </c>
       <c r="E134" s="2"/>
-      <c r="F134" s="35"/>
-      <c r="G134" s="58"/>
-      <c r="H134" s="58">
+      <c r="F134" s="34"/>
+      <c r="G134" s="57"/>
+      <c r="H134" s="57">
         <f>E134*G134</f>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B135" s="32"/>
-      <c r="C135" s="39"/>
-      <c r="D135" s="32"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="38"/>
+      <c r="D135" s="31"/>
       <c r="E135" s="2"/>
-      <c r="F135" s="35"/>
-      <c r="G135" s="58"/>
-      <c r="H135" s="58"/>
+      <c r="F135" s="34"/>
+      <c r="G135" s="57"/>
+      <c r="H135" s="57"/>
     </row>
     <row r="136" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B136" s="32"/>
-      <c r="C136" s="39"/>
-      <c r="D136" s="32"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="38"/>
+      <c r="D136" s="31"/>
       <c r="E136" s="2"/>
-      <c r="F136" s="35"/>
-      <c r="G136" s="58"/>
-      <c r="H136" s="58"/>
+      <c r="F136" s="34"/>
+      <c r="G136" s="57"/>
+      <c r="H136" s="57"/>
     </row>
     <row r="137" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="48"/>
-      <c r="B137" s="138" t="s">
-        <v>121</v>
-      </c>
-      <c r="C137" s="136"/>
-      <c r="D137" s="137"/>
-      <c r="E137" s="49"/>
-      <c r="F137" s="50"/>
-      <c r="G137" s="51"/>
-      <c r="H137" s="49">
+      <c r="A137" s="47"/>
+      <c r="B137" s="139" t="s">
+        <v>137</v>
+      </c>
+      <c r="C137" s="137"/>
+      <c r="D137" s="138"/>
+      <c r="E137" s="48"/>
+      <c r="F137" s="49"/>
+      <c r="G137" s="50"/>
+      <c r="H137" s="48">
         <f>SUM(H138:H140)</f>
         <v>0</v>
       </c>
-      <c r="I137" s="52"/>
-      <c r="J137" s="48"/>
-      <c r="K137" s="48"/>
-      <c r="L137" s="48"/>
-      <c r="M137" s="48"/>
-      <c r="N137" s="48"/>
-      <c r="O137" s="48"/>
-      <c r="P137" s="48"/>
-      <c r="Q137" s="48"/>
-      <c r="R137" s="48"/>
-      <c r="S137" s="48"/>
-      <c r="T137" s="48"/>
-      <c r="U137" s="48"/>
-      <c r="V137" s="48"/>
-      <c r="W137" s="48"/>
-      <c r="X137" s="48"/>
-      <c r="Y137" s="48"/>
-      <c r="Z137" s="48"/>
+      <c r="I137" s="51"/>
+      <c r="J137" s="47"/>
+      <c r="K137" s="47"/>
+      <c r="L137" s="47"/>
+      <c r="M137" s="47"/>
+      <c r="N137" s="47"/>
+      <c r="O137" s="47"/>
+      <c r="P137" s="47"/>
+      <c r="Q137" s="47"/>
+      <c r="R137" s="47"/>
+      <c r="S137" s="47"/>
+      <c r="T137" s="47"/>
+      <c r="U137" s="47"/>
+      <c r="V137" s="47"/>
+      <c r="W137" s="47"/>
+      <c r="X137" s="47"/>
+      <c r="Y137" s="47"/>
+      <c r="Z137" s="47"/>
     </row>
     <row r="138" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B138" s="32"/>
-      <c r="C138" s="39"/>
-      <c r="D138" s="32" t="s">
-        <v>120</v>
+      <c r="B138" s="31"/>
+      <c r="C138" s="38"/>
+      <c r="D138" s="31" t="s">
+        <v>136</v>
       </c>
       <c r="E138" s="2"/>
-      <c r="F138" s="35"/>
-      <c r="G138" s="58"/>
-      <c r="H138" s="58">
+      <c r="F138" s="34"/>
+      <c r="G138" s="57"/>
+      <c r="H138" s="57">
         <f t="shared" ref="H138:H140" si="8">E138*G138</f>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B139" s="32"/>
-      <c r="C139" s="39"/>
-      <c r="D139" s="32"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="38"/>
+      <c r="D139" s="31"/>
       <c r="E139" s="2"/>
-      <c r="F139" s="35"/>
-      <c r="G139" s="58"/>
-      <c r="H139" s="58">
+      <c r="F139" s="34"/>
+      <c r="G139" s="57"/>
+      <c r="H139" s="57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B140" s="32"/>
-      <c r="C140" s="39"/>
-      <c r="D140" s="32"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="38"/>
+      <c r="D140" s="31"/>
       <c r="E140" s="2"/>
-      <c r="F140" s="35"/>
-      <c r="G140" s="58"/>
-      <c r="H140" s="58">
+      <c r="F140" s="34"/>
+      <c r="G140" s="57"/>
+      <c r="H140" s="57">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B141" s="32"/>
-      <c r="C141" s="39"/>
-      <c r="D141" s="32"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="38"/>
+      <c r="D141" s="31"/>
       <c r="E141" s="2"/>
-      <c r="F141" s="35"/>
+      <c r="F141" s="34"/>
       <c r="G141" s="2"/>
-      <c r="H141" s="58"/>
+      <c r="H141" s="57"/>
     </row>
     <row r="142" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="48"/>
-      <c r="B142" s="138" t="s">
-        <v>122</v>
-      </c>
-      <c r="C142" s="136"/>
-      <c r="D142" s="137"/>
-      <c r="E142" s="49"/>
-      <c r="F142" s="50"/>
-      <c r="G142" s="51"/>
-      <c r="H142" s="49">
+      <c r="A142" s="47"/>
+      <c r="B142" s="139" t="s">
+        <v>138</v>
+      </c>
+      <c r="C142" s="137"/>
+      <c r="D142" s="138"/>
+      <c r="E142" s="48"/>
+      <c r="F142" s="49"/>
+      <c r="G142" s="50"/>
+      <c r="H142" s="48">
         <f>SUM(H143:H148)</f>
-        <v>27835</v>
-      </c>
-      <c r="I142" s="52"/>
-      <c r="J142" s="48"/>
-      <c r="K142" s="48"/>
-      <c r="L142" s="48"/>
-      <c r="M142" s="48"/>
-      <c r="N142" s="48"/>
-      <c r="O142" s="48"/>
-      <c r="P142" s="48"/>
-      <c r="Q142" s="48"/>
-      <c r="R142" s="48"/>
-      <c r="S142" s="48"/>
-      <c r="T142" s="48"/>
-      <c r="U142" s="48"/>
-      <c r="V142" s="48"/>
-      <c r="W142" s="48"/>
-      <c r="X142" s="48"/>
-      <c r="Y142" s="48"/>
-      <c r="Z142" s="48"/>
+        <v>31635</v>
+      </c>
+      <c r="I142" s="51"/>
+      <c r="J142" s="47"/>
+      <c r="K142" s="47"/>
+      <c r="L142" s="47"/>
+      <c r="M142" s="47"/>
+      <c r="N142" s="47"/>
+      <c r="O142" s="47"/>
+      <c r="P142" s="47"/>
+      <c r="Q142" s="47"/>
+      <c r="R142" s="47"/>
+      <c r="S142" s="47"/>
+      <c r="T142" s="47"/>
+      <c r="U142" s="47"/>
+      <c r="V142" s="47"/>
+      <c r="W142" s="47"/>
+      <c r="X142" s="47"/>
+      <c r="Y142" s="47"/>
+      <c r="Z142" s="47"/>
     </row>
     <row r="143" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B143" s="32"/>
-      <c r="C143" s="39"/>
-      <c r="D143" s="32" t="s">
-        <v>123</v>
+      <c r="B143" s="31"/>
+      <c r="C143" s="38"/>
+      <c r="D143" s="31" t="s">
+        <v>139</v>
       </c>
       <c r="E143" s="2"/>
-      <c r="F143" s="35"/>
-      <c r="G143" s="58"/>
-      <c r="H143" s="56">
-        <v>22800</v>
-      </c>
-      <c r="I143" s="66"/>
-      <c r="J143" s="66"/>
-      <c r="K143" s="66"/>
-      <c r="L143" s="66"/>
+      <c r="F143" s="34"/>
+      <c r="G143" s="57"/>
+      <c r="H143" s="150">
+        <v>26600</v>
+      </c>
+      <c r="I143" s="95" t="s">
+        <v>140</v>
+      </c>
+      <c r="J143" s="95"/>
+      <c r="K143" s="95"/>
+      <c r="L143" s="95"/>
+      <c r="M143" s="60"/>
     </row>
     <row r="144" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B144" s="32"/>
-      <c r="C144" s="39"/>
-      <c r="D144" s="32" t="s">
-        <v>124</v>
+      <c r="B144" s="31"/>
+      <c r="C144" s="38"/>
+      <c r="D144" s="31" t="s">
+        <v>141</v>
       </c>
       <c r="E144" s="2"/>
-      <c r="F144" s="35"/>
-      <c r="G144" s="58"/>
-      <c r="H144" s="56">
+      <c r="F144" s="34"/>
+      <c r="G144" s="57"/>
+      <c r="H144" s="55">
         <v>875</v>
       </c>
-      <c r="I144" s="66"/>
-      <c r="J144" s="66"/>
-      <c r="K144" s="66"/>
-      <c r="L144" s="66"/>
+      <c r="I144" s="72"/>
+      <c r="J144" s="72"/>
+      <c r="K144" s="72"/>
+      <c r="L144" s="72"/>
     </row>
     <row r="145" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B145" s="32"/>
-      <c r="C145" s="39"/>
-      <c r="D145" s="32" t="s">
-        <v>125</v>
+      <c r="B145" s="31"/>
+      <c r="C145" s="38"/>
+      <c r="D145" s="31" t="s">
+        <v>142</v>
       </c>
       <c r="E145" s="2"/>
-      <c r="F145" s="35"/>
-      <c r="G145" s="58"/>
-      <c r="H145" s="58">
+      <c r="F145" s="34"/>
+      <c r="G145" s="57"/>
+      <c r="H145" s="57">
         <f>E145*G145</f>
         <v>0</v>
       </c>
-      <c r="I145" s="66"/>
-      <c r="J145" s="66"/>
-      <c r="K145" s="66"/>
-      <c r="L145" s="66"/>
+      <c r="I145" s="72"/>
+      <c r="J145" s="72"/>
+      <c r="K145" s="72"/>
+      <c r="L145" s="72"/>
     </row>
     <row r="146" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B146" s="32"/>
-      <c r="C146" s="39"/>
-      <c r="D146" s="39" t="s">
-        <v>126</v>
+      <c r="B146" s="31"/>
+      <c r="C146" s="38"/>
+      <c r="D146" s="38" t="s">
+        <v>143</v>
       </c>
       <c r="E146" s="2"/>
-      <c r="F146" s="35"/>
-      <c r="G146" s="58"/>
-      <c r="H146" s="56">
+      <c r="F146" s="34"/>
+      <c r="G146" s="57"/>
+      <c r="H146" s="55">
         <v>2000</v>
       </c>
-      <c r="I146" s="66"/>
-      <c r="J146" s="66"/>
-      <c r="K146" s="66"/>
-      <c r="L146" s="66"/>
+      <c r="I146" s="72"/>
+      <c r="J146" s="72"/>
+      <c r="K146" s="72"/>
+      <c r="L146" s="72"/>
     </row>
     <row r="147" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B147" s="32"/>
-      <c r="C147" s="39"/>
-      <c r="D147" s="39" t="s">
-        <v>127</v>
+      <c r="B147" s="31"/>
+      <c r="C147" s="38"/>
+      <c r="D147" s="38" t="s">
+        <v>144</v>
       </c>
       <c r="E147" s="2"/>
-      <c r="F147" s="35"/>
-      <c r="G147" s="58"/>
-      <c r="H147" s="56">
+      <c r="F147" s="34"/>
+      <c r="G147" s="57"/>
+      <c r="H147" s="55">
         <v>1200</v>
       </c>
-      <c r="I147" s="66"/>
-      <c r="J147" s="66"/>
-      <c r="K147" s="66"/>
-      <c r="L147" s="66"/>
+      <c r="I147" s="72"/>
+      <c r="J147" s="72"/>
+      <c r="K147" s="72"/>
+      <c r="L147" s="72"/>
     </row>
     <row r="148" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B148" s="32"/>
-      <c r="C148" s="39"/>
-      <c r="D148" s="32" t="s">
-        <v>128</v>
+      <c r="B148" s="31"/>
+      <c r="C148" s="38"/>
+      <c r="D148" s="31" t="s">
+        <v>145</v>
       </c>
       <c r="E148" s="2"/>
-      <c r="F148" s="35"/>
+      <c r="F148" s="34"/>
       <c r="G148" s="2"/>
-      <c r="H148" s="58">
+      <c r="H148" s="57">
         <v>960</v>
       </c>
-      <c r="I148" s="66"/>
-      <c r="J148" s="66"/>
-      <c r="K148" s="66"/>
-      <c r="L148" s="66"/>
+      <c r="I148" s="72"/>
+      <c r="J148" s="72"/>
+      <c r="K148" s="72"/>
+      <c r="L148" s="72"/>
     </row>
     <row r="149" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="48"/>
-      <c r="B149" s="138" t="s">
-        <v>129</v>
-      </c>
-      <c r="C149" s="136"/>
-      <c r="D149" s="137"/>
-      <c r="E149" s="49"/>
-      <c r="F149" s="50"/>
-      <c r="G149" s="51"/>
-      <c r="H149" s="49">
+      <c r="A149" s="47"/>
+      <c r="B149" s="139" t="s">
+        <v>146</v>
+      </c>
+      <c r="C149" s="137"/>
+      <c r="D149" s="138"/>
+      <c r="E149" s="48"/>
+      <c r="F149" s="49"/>
+      <c r="G149" s="50"/>
+      <c r="H149" s="48">
         <f>SUM(H150:H157)</f>
         <v>21520</v>
       </c>
-      <c r="I149" s="52"/>
-      <c r="J149" s="48"/>
-      <c r="K149" s="48"/>
-      <c r="L149" s="48"/>
-      <c r="M149" s="48"/>
-      <c r="N149" s="48"/>
-      <c r="O149" s="48"/>
-      <c r="P149" s="48"/>
-      <c r="Q149" s="48"/>
-      <c r="R149" s="48"/>
-      <c r="S149" s="48"/>
-      <c r="T149" s="48"/>
-      <c r="U149" s="48"/>
-      <c r="V149" s="48"/>
-      <c r="W149" s="48"/>
-      <c r="X149" s="48"/>
-      <c r="Y149" s="48"/>
-      <c r="Z149" s="48"/>
+      <c r="I149" s="51"/>
+      <c r="J149" s="47"/>
+      <c r="K149" s="47"/>
+      <c r="L149" s="47"/>
+      <c r="M149" s="47"/>
+      <c r="N149" s="47"/>
+      <c r="O149" s="47"/>
+      <c r="P149" s="47"/>
+      <c r="Q149" s="47"/>
+      <c r="R149" s="47"/>
+      <c r="S149" s="47"/>
+      <c r="T149" s="47"/>
+      <c r="U149" s="47"/>
+      <c r="V149" s="47"/>
+      <c r="W149" s="47"/>
+      <c r="X149" s="47"/>
+      <c r="Y149" s="47"/>
+      <c r="Z149" s="47"/>
     </row>
     <row r="150" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B150" s="32"/>
-      <c r="C150" s="39"/>
-      <c r="D150" s="33" t="s">
-        <v>130</v>
+      <c r="B150" s="31"/>
+      <c r="C150" s="38"/>
+      <c r="D150" s="32" t="s">
+        <v>147</v>
       </c>
       <c r="E150" s="2"/>
-      <c r="F150" s="35"/>
-      <c r="G150" s="58"/>
-      <c r="H150" s="58">
+      <c r="F150" s="34"/>
+      <c r="G150" s="57"/>
+      <c r="H150" s="57">
         <v>19750</v>
       </c>
-      <c r="I150" s="66"/>
-      <c r="J150" s="66"/>
-      <c r="K150" s="66"/>
+      <c r="I150" s="72"/>
+      <c r="J150" s="72"/>
+      <c r="K150" s="72"/>
     </row>
     <row r="151" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B151" s="32"/>
-      <c r="C151" s="39"/>
-      <c r="D151" s="85" t="s">
-        <v>131</v>
+      <c r="B151" s="31"/>
+      <c r="C151" s="38"/>
+      <c r="D151" s="94" t="s">
+        <v>148</v>
       </c>
       <c r="E151" s="2"/>
-      <c r="F151" s="35"/>
-      <c r="G151" s="58"/>
-      <c r="H151" s="58"/>
-      <c r="I151" s="66"/>
-      <c r="J151" s="66"/>
-      <c r="K151" s="66"/>
+      <c r="F151" s="34"/>
+      <c r="G151" s="57"/>
+      <c r="H151" s="57"/>
+      <c r="I151" s="72"/>
+      <c r="J151" s="72"/>
+      <c r="K151" s="72"/>
     </row>
     <row r="152" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B152" s="32"/>
-      <c r="C152" s="39"/>
-      <c r="D152" s="85" t="s">
-        <v>132</v>
+      <c r="B152" s="31"/>
+      <c r="C152" s="38"/>
+      <c r="D152" s="94" t="s">
+        <v>149</v>
       </c>
       <c r="E152" s="2"/>
-      <c r="F152" s="35"/>
-      <c r="G152" s="58"/>
-      <c r="H152" s="58"/>
-      <c r="I152" s="66"/>
-      <c r="J152" s="66"/>
-      <c r="K152" s="66"/>
+      <c r="F152" s="34"/>
+      <c r="G152" s="57"/>
+      <c r="H152" s="57"/>
+      <c r="I152" s="72"/>
+      <c r="J152" s="72"/>
+      <c r="K152" s="72"/>
     </row>
     <row r="153" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B153" s="32"/>
-      <c r="C153" s="39"/>
-      <c r="D153" s="85" t="s">
-        <v>133</v>
+      <c r="B153" s="31"/>
+      <c r="C153" s="38"/>
+      <c r="D153" s="94" t="s">
+        <v>150</v>
       </c>
       <c r="E153" s="2"/>
-      <c r="F153" s="35"/>
-      <c r="G153" s="58"/>
-      <c r="H153" s="58"/>
-      <c r="I153" s="66"/>
-      <c r="J153" s="66"/>
-      <c r="K153" s="66"/>
+      <c r="F153" s="34"/>
+      <c r="G153" s="57"/>
+      <c r="H153" s="57"/>
+      <c r="I153" s="72"/>
+      <c r="J153" s="72"/>
+      <c r="K153" s="72"/>
     </row>
     <row r="154" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B154" s="32"/>
-      <c r="C154" s="39"/>
-      <c r="D154" s="85" t="s">
-        <v>134</v>
+      <c r="B154" s="31"/>
+      <c r="C154" s="38"/>
+      <c r="D154" s="94" t="s">
+        <v>151</v>
       </c>
       <c r="E154" s="2"/>
-      <c r="F154" s="35"/>
-      <c r="G154" s="58"/>
-      <c r="H154" s="58"/>
-      <c r="I154" s="66"/>
-      <c r="J154" s="66"/>
-      <c r="K154" s="66"/>
+      <c r="F154" s="34"/>
+      <c r="G154" s="57"/>
+      <c r="H154" s="57"/>
+      <c r="I154" s="72"/>
+      <c r="J154" s="72"/>
+      <c r="K154" s="72"/>
     </row>
     <row r="155" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B155" s="32"/>
-      <c r="C155" s="39"/>
-      <c r="D155" s="86" t="s">
-        <v>135</v>
+      <c r="B155" s="31"/>
+      <c r="C155" s="38"/>
+      <c r="D155" s="96" t="s">
+        <v>152</v>
       </c>
       <c r="E155" s="2"/>
-      <c r="F155" s="35"/>
-      <c r="G155" s="58"/>
-      <c r="H155" s="58">
+      <c r="F155" s="34"/>
+      <c r="G155" s="57"/>
+      <c r="H155" s="57">
         <f>E155*G155</f>
         <v>0</v>
       </c>
-      <c r="I155" s="66"/>
-      <c r="J155" s="66"/>
-      <c r="K155" s="66"/>
+      <c r="I155" s="95" t="s">
+        <v>153</v>
+      </c>
+      <c r="J155" s="95"/>
+      <c r="K155" s="95"/>
+      <c r="L155" s="60"/>
     </row>
     <row r="156" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B156" s="32"/>
-      <c r="C156" s="39"/>
-      <c r="D156" s="32" t="s">
-        <v>136</v>
+      <c r="B156" s="31"/>
+      <c r="C156" s="38"/>
+      <c r="D156" s="31" t="s">
+        <v>154</v>
       </c>
       <c r="E156" s="2"/>
-      <c r="F156" s="35"/>
-      <c r="G156" s="58"/>
-      <c r="H156" s="56">
+      <c r="F156" s="34"/>
+      <c r="G156" s="57"/>
+      <c r="H156" s="55">
         <v>570</v>
       </c>
-      <c r="I156" s="66"/>
-      <c r="J156" s="66"/>
-      <c r="K156" s="66"/>
+      <c r="I156" s="72"/>
+      <c r="J156" s="72"/>
+      <c r="K156" s="72"/>
     </row>
     <row r="157" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B157" s="32"/>
-      <c r="C157" s="39"/>
-      <c r="D157" s="39" t="s">
-        <v>137</v>
+      <c r="B157" s="31"/>
+      <c r="C157" s="38"/>
+      <c r="D157" s="38" t="s">
+        <v>155</v>
       </c>
       <c r="E157" s="2"/>
-      <c r="F157" s="35"/>
-      <c r="G157" s="58"/>
-      <c r="H157" s="56">
+      <c r="F157" s="34"/>
+      <c r="G157" s="57"/>
+      <c r="H157" s="55">
         <v>1200</v>
       </c>
-      <c r="I157" s="66"/>
-      <c r="J157" s="66"/>
-      <c r="K157" s="66"/>
+      <c r="I157" s="72"/>
+      <c r="J157" s="72"/>
+      <c r="K157" s="72"/>
     </row>
     <row r="158" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B158" s="32"/>
-      <c r="C158" s="39"/>
-      <c r="D158" s="39"/>
+      <c r="B158" s="31"/>
+      <c r="C158" s="38"/>
+      <c r="D158" s="38"/>
       <c r="E158" s="2"/>
-      <c r="F158" s="35"/>
-      <c r="G158" s="58"/>
-      <c r="H158" s="58"/>
+      <c r="F158" s="34"/>
+      <c r="G158" s="57"/>
+      <c r="H158" s="57"/>
     </row>
     <row r="159" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="48"/>
-      <c r="B159" s="138" t="s">
-        <v>138</v>
-      </c>
-      <c r="C159" s="136"/>
-      <c r="D159" s="137"/>
-      <c r="E159" s="49"/>
-      <c r="F159" s="50"/>
-      <c r="G159" s="51"/>
-      <c r="H159" s="49">
+      <c r="A159" s="47"/>
+      <c r="B159" s="139" t="s">
+        <v>156</v>
+      </c>
+      <c r="C159" s="137"/>
+      <c r="D159" s="138"/>
+      <c r="E159" s="48"/>
+      <c r="F159" s="49"/>
+      <c r="G159" s="50"/>
+      <c r="H159" s="48">
         <f>SUM(H160:H166)</f>
-        <v>125275</v>
-      </c>
-      <c r="I159" s="87"/>
-      <c r="J159" s="88"/>
-      <c r="K159" s="88"/>
-      <c r="L159" s="88"/>
-      <c r="M159" s="88"/>
-      <c r="N159" s="89"/>
-      <c r="O159" s="48"/>
-      <c r="P159" s="48"/>
-      <c r="Q159" s="48"/>
-      <c r="R159" s="48"/>
-      <c r="S159" s="48"/>
-      <c r="T159" s="48"/>
-      <c r="U159" s="48"/>
-      <c r="V159" s="48"/>
-      <c r="W159" s="48"/>
-      <c r="X159" s="48"/>
-      <c r="Y159" s="48"/>
-      <c r="Z159" s="48"/>
+        <v>117275</v>
+      </c>
+      <c r="I159" s="97"/>
+      <c r="J159" s="98"/>
+      <c r="K159" s="98"/>
+      <c r="L159" s="98"/>
+      <c r="M159" s="98"/>
+      <c r="N159" s="99"/>
+      <c r="O159" s="47"/>
+      <c r="P159" s="47"/>
+      <c r="Q159" s="47"/>
+      <c r="R159" s="47"/>
+      <c r="S159" s="47"/>
+      <c r="T159" s="47"/>
+      <c r="U159" s="47"/>
+      <c r="V159" s="47"/>
+      <c r="W159" s="47"/>
+      <c r="X159" s="47"/>
+      <c r="Y159" s="47"/>
+      <c r="Z159" s="47"/>
     </row>
     <row r="160" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B160" s="32"/>
-      <c r="C160" s="39"/>
-      <c r="D160" s="82" t="s">
-        <v>139</v>
+      <c r="B160" s="31"/>
+      <c r="C160" s="38"/>
+      <c r="D160" s="91" t="s">
+        <v>157</v>
       </c>
       <c r="E160" s="2"/>
-      <c r="F160" s="35"/>
-      <c r="G160" s="58"/>
-      <c r="H160" s="56">
-        <v>119875</v>
-      </c>
-      <c r="I160" s="65"/>
-      <c r="J160" s="65"/>
-      <c r="K160" s="65"/>
-      <c r="L160" s="65"/>
-      <c r="M160" s="65"/>
-      <c r="N160" s="65"/>
+      <c r="F160" s="34"/>
+      <c r="G160" s="57"/>
+      <c r="H160" s="55">
+        <v>111875</v>
+      </c>
+      <c r="I160" s="155" t="s">
+        <v>218</v>
+      </c>
+      <c r="J160" s="100"/>
+      <c r="K160" s="156"/>
+      <c r="L160" s="157"/>
+      <c r="M160" s="157"/>
+      <c r="N160" s="69"/>
     </row>
     <row r="161" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B161" s="32"/>
-      <c r="C161" s="39"/>
-      <c r="D161" s="32" t="s">
-        <v>140</v>
+      <c r="B161" s="31"/>
+      <c r="C161" s="38"/>
+      <c r="D161" s="31" t="s">
+        <v>158</v>
       </c>
       <c r="E161" s="2"/>
-      <c r="F161" s="35"/>
-      <c r="G161" s="58"/>
-      <c r="H161" s="58">
+      <c r="F161" s="34"/>
+      <c r="G161" s="57"/>
+      <c r="H161" s="57">
         <f t="shared" ref="H161:H162" si="9">E161*G161</f>
         <v>0</v>
       </c>
-      <c r="L161" s="65"/>
+      <c r="L161" s="69"/>
     </row>
     <row r="162" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B162" s="32"/>
-      <c r="C162" s="39"/>
-      <c r="D162" s="32" t="s">
-        <v>141</v>
+      <c r="B162" s="31"/>
+      <c r="C162" s="38"/>
+      <c r="D162" s="31" t="s">
+        <v>159</v>
       </c>
       <c r="E162" s="2"/>
-      <c r="F162" s="35"/>
-      <c r="G162" s="58"/>
-      <c r="H162" s="58">
+      <c r="F162" s="34"/>
+      <c r="G162" s="57"/>
+      <c r="H162" s="57">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L162" s="65"/>
+      <c r="L162" s="69"/>
     </row>
     <row r="163" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B163" s="32"/>
-      <c r="C163" s="39"/>
-      <c r="D163" s="32" t="s">
-        <v>142</v>
+      <c r="B163" s="31"/>
+      <c r="C163" s="38"/>
+      <c r="D163" s="31" t="s">
+        <v>160</v>
       </c>
       <c r="E163" s="2"/>
-      <c r="F163" s="35"/>
-      <c r="G163" s="58"/>
-      <c r="H163" s="56">
+      <c r="F163" s="34"/>
+      <c r="G163" s="57"/>
+      <c r="H163" s="55">
         <v>3600</v>
       </c>
-      <c r="L163" s="65"/>
+      <c r="L163" s="69"/>
     </row>
     <row r="164" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B164" s="32"/>
-      <c r="C164" s="39"/>
-      <c r="D164" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="E164" s="90" t="s">
+      <c r="B164" s="31"/>
+      <c r="C164" s="38"/>
+      <c r="D164" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="E164" s="101" t="s">
+        <v>162</v>
+      </c>
+      <c r="F164" s="102"/>
+      <c r="G164" s="103"/>
+      <c r="H164" s="57">
+        <v>0</v>
+      </c>
+      <c r="I164" s="69"/>
+    </row>
+    <row r="165" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B165" s="31"/>
+      <c r="C165" s="38"/>
+      <c r="D165" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="E165" s="2"/>
+      <c r="F165" s="34"/>
+      <c r="G165" s="57"/>
+      <c r="H165" s="55">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="166" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B166" s="31"/>
+      <c r="C166" s="38"/>
+      <c r="D166" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="F164" s="91"/>
-      <c r="G164" s="92"/>
-      <c r="H164" s="58">
-        <v>0</v>
-      </c>
-      <c r="I164" s="65"/>
-    </row>
-    <row r="165" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B165" s="32"/>
-      <c r="C165" s="39"/>
-      <c r="D165" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="E165" s="2"/>
-      <c r="F165" s="35"/>
-      <c r="G165" s="58"/>
-      <c r="H165" s="56">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="166" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B166" s="32"/>
-      <c r="C166" s="39"/>
-      <c r="D166" s="39" t="s">
-        <v>127</v>
-      </c>
       <c r="E166" s="2"/>
-      <c r="F166" s="35"/>
-      <c r="G166" s="58"/>
-      <c r="H166" s="58">
+      <c r="F166" s="34"/>
+      <c r="G166" s="57"/>
+      <c r="H166" s="57">
         <f>E166*G166</f>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B167" s="32"/>
-      <c r="C167" s="39"/>
-      <c r="D167" s="32"/>
+      <c r="B167" s="31"/>
+      <c r="C167" s="38"/>
+      <c r="D167" s="31"/>
       <c r="E167" s="2"/>
-      <c r="F167" s="35"/>
+      <c r="F167" s="34"/>
       <c r="G167" s="2"/>
-      <c r="H167" s="58"/>
+      <c r="H167" s="57"/>
     </row>
     <row r="168" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="48"/>
-      <c r="B168" s="138" t="s">
-        <v>146</v>
-      </c>
-      <c r="C168" s="136"/>
-      <c r="D168" s="137"/>
-      <c r="E168" s="49"/>
-      <c r="F168" s="50"/>
-      <c r="G168" s="51"/>
-      <c r="H168" s="49">
+      <c r="A168" s="47"/>
+      <c r="B168" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="C168" s="137"/>
+      <c r="D168" s="138"/>
+      <c r="E168" s="48"/>
+      <c r="F168" s="49"/>
+      <c r="G168" s="50"/>
+      <c r="H168" s="48">
         <f>SUM(H169:H187)</f>
-        <v>130218</v>
-      </c>
-      <c r="I168" s="52"/>
-      <c r="J168" s="48"/>
-      <c r="K168" s="48"/>
-      <c r="L168" s="48"/>
-      <c r="M168" s="48"/>
-      <c r="N168" s="48"/>
-      <c r="O168" s="48"/>
-      <c r="P168" s="48"/>
-      <c r="Q168" s="48"/>
-      <c r="R168" s="48"/>
-      <c r="S168" s="48"/>
-      <c r="T168" s="48"/>
-      <c r="U168" s="48"/>
-      <c r="V168" s="48"/>
-      <c r="W168" s="48"/>
-      <c r="X168" s="48"/>
-      <c r="Y168" s="48"/>
-      <c r="Z168" s="48"/>
+        <v>144905</v>
+      </c>
+      <c r="I168" s="51"/>
+      <c r="J168" s="47"/>
+      <c r="K168" s="47"/>
+      <c r="L168" s="47"/>
+      <c r="M168" s="47"/>
+      <c r="N168" s="47"/>
+      <c r="O168" s="47"/>
+      <c r="P168" s="47"/>
+      <c r="Q168" s="47"/>
+      <c r="R168" s="47"/>
+      <c r="S168" s="47"/>
+      <c r="T168" s="47"/>
+      <c r="U168" s="47"/>
+      <c r="V168" s="47"/>
+      <c r="W168" s="47"/>
+      <c r="X168" s="47"/>
+      <c r="Y168" s="47"/>
+      <c r="Z168" s="47"/>
     </row>
     <row r="169" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B169" s="32"/>
-      <c r="C169" s="39"/>
-      <c r="D169" s="32" t="s">
-        <v>147</v>
+      <c r="B169" s="31"/>
+      <c r="C169" s="38"/>
+      <c r="D169" s="31" t="s">
+        <v>165</v>
       </c>
       <c r="E169" s="2"/>
-      <c r="F169" s="35"/>
-      <c r="G169" s="58"/>
-      <c r="H169" s="126">
+      <c r="F169" s="34"/>
+      <c r="G169" s="57"/>
+      <c r="H169" s="55">
         <v>92165</v>
       </c>
-      <c r="I169" s="66"/>
-      <c r="J169" s="66"/>
-      <c r="K169" s="66"/>
+      <c r="I169" s="95" t="s">
+        <v>166</v>
+      </c>
+      <c r="J169" s="95"/>
+      <c r="K169" s="95"/>
+      <c r="L169" s="60"/>
+      <c r="M169" s="60"/>
     </row>
     <row r="170" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B170" s="32"/>
-      <c r="C170" s="39"/>
-      <c r="D170" s="32" t="s">
-        <v>148</v>
+      <c r="B170" s="31"/>
+      <c r="C170" s="38"/>
+      <c r="D170" s="31" t="s">
+        <v>167</v>
       </c>
       <c r="E170" s="2"/>
-      <c r="F170" s="93"/>
-      <c r="G170" s="58"/>
-      <c r="H170" s="58">
+      <c r="F170" s="104"/>
+      <c r="G170" s="57"/>
+      <c r="H170" s="57">
         <v>0</v>
       </c>
-      <c r="I170" s="66"/>
-      <c r="J170" s="66"/>
-      <c r="K170" s="66"/>
+      <c r="I170" s="72"/>
+      <c r="J170" s="72"/>
+      <c r="K170" s="72"/>
     </row>
     <row r="171" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B171" s="32"/>
-      <c r="C171" s="39"/>
-      <c r="D171" s="32" t="s">
-        <v>149</v>
+      <c r="B171" s="31"/>
+      <c r="C171" s="38"/>
+      <c r="D171" s="31" t="s">
+        <v>168</v>
       </c>
       <c r="E171" s="2"/>
-      <c r="F171" s="35"/>
-      <c r="G171" s="58"/>
-      <c r="H171" s="58">
+      <c r="F171" s="34"/>
+      <c r="G171" s="57"/>
+      <c r="H171" s="57">
         <v>0</v>
       </c>
-      <c r="I171" s="66"/>
-      <c r="J171" s="66"/>
-      <c r="K171" s="66"/>
+      <c r="I171" s="72"/>
+      <c r="J171" s="72"/>
+      <c r="K171" s="72"/>
     </row>
     <row r="172" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B172" s="32"/>
-      <c r="C172" s="39"/>
-      <c r="D172" s="32" t="s">
-        <v>150</v>
+      <c r="B172" s="31"/>
+      <c r="C172" s="38"/>
+      <c r="D172" s="31" t="s">
+        <v>169</v>
       </c>
       <c r="E172" s="2"/>
-      <c r="F172" s="35"/>
-      <c r="G172" s="58"/>
-      <c r="H172" s="56">
+      <c r="F172" s="34"/>
+      <c r="G172" s="57"/>
+      <c r="H172" s="55">
         <v>6775</v>
       </c>
-      <c r="I172" s="66"/>
-      <c r="J172" s="66"/>
-      <c r="K172" s="66"/>
+      <c r="I172" s="72"/>
+      <c r="J172" s="72"/>
+      <c r="K172" s="72"/>
     </row>
     <row r="173" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B173" s="32"/>
-      <c r="C173" s="39"/>
-      <c r="D173" s="32" t="s">
-        <v>151</v>
+      <c r="B173" s="31"/>
+      <c r="C173" s="38"/>
+      <c r="D173" s="31" t="s">
+        <v>170</v>
       </c>
       <c r="E173" s="2"/>
-      <c r="F173" s="35"/>
-      <c r="G173" s="58"/>
-      <c r="H173" s="58">
+      <c r="F173" s="34"/>
+      <c r="G173" s="57"/>
+      <c r="H173" s="57">
         <v>0</v>
       </c>
-      <c r="I173" s="66"/>
-      <c r="J173" s="66"/>
-      <c r="K173" s="66"/>
+      <c r="I173" s="72"/>
+      <c r="J173" s="72"/>
+      <c r="K173" s="72"/>
     </row>
     <row r="174" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B174" s="32"/>
-      <c r="C174" s="39"/>
-      <c r="D174" s="32" t="s">
-        <v>152</v>
+      <c r="B174" s="31"/>
+      <c r="C174" s="38"/>
+      <c r="D174" s="31" t="s">
+        <v>171</v>
       </c>
       <c r="E174" s="2"/>
-      <c r="F174" s="35"/>
-      <c r="G174" s="58"/>
-      <c r="H174" s="58">
+      <c r="F174" s="34"/>
+      <c r="G174" s="57"/>
+      <c r="H174" s="57">
         <v>0</v>
       </c>
-      <c r="I174" s="66"/>
-      <c r="J174" s="66"/>
-      <c r="K174" s="78"/>
+      <c r="I174" s="72"/>
+      <c r="J174" s="72"/>
+      <c r="K174" s="105"/>
     </row>
     <row r="175" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B175" s="32"/>
-      <c r="C175" s="39"/>
-      <c r="D175" s="124" t="s">
-        <v>196</v>
+      <c r="B175" s="31"/>
+      <c r="C175" s="38"/>
+      <c r="D175" s="82" t="s">
+        <v>172</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
-      <c r="H175" s="56">
+      <c r="H175" s="55">
         <v>5925</v>
       </c>
-      <c r="I175" s="66"/>
-      <c r="J175" s="66"/>
-      <c r="K175" s="66"/>
+      <c r="I175" s="72"/>
+      <c r="J175" s="72"/>
+      <c r="K175" s="72"/>
     </row>
     <row r="176" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B176" s="32"/>
-      <c r="C176" s="39"/>
-      <c r="D176" s="73" t="s">
-        <v>153</v>
-      </c>
-      <c r="E176" s="94"/>
+      <c r="B176" s="31"/>
+      <c r="C176" s="38"/>
+      <c r="D176" s="82" t="s">
+        <v>173</v>
+      </c>
+      <c r="E176" s="106"/>
       <c r="F176" s="2"/>
-      <c r="H176" s="58">
+      <c r="H176" s="57">
         <v>0</v>
       </c>
-      <c r="I176" s="66"/>
-      <c r="J176" s="66"/>
-      <c r="K176" s="66"/>
-    </row>
-    <row r="177" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B177" s="32"/>
-      <c r="C177" s="39"/>
-      <c r="D177" s="32" t="s">
-        <v>154</v>
+      <c r="I176" s="72"/>
+      <c r="J176" s="72"/>
+      <c r="K176" s="72"/>
+    </row>
+    <row r="177" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B177" s="31"/>
+      <c r="C177" s="38"/>
+      <c r="D177" s="31" t="s">
+        <v>174</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
-      <c r="H177" s="58">
+      <c r="H177" s="57">
         <v>0</v>
       </c>
-      <c r="I177" s="66"/>
-      <c r="J177" s="66"/>
-      <c r="K177" s="66"/>
-    </row>
-    <row r="178" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B178" s="32"/>
-      <c r="C178" s="39"/>
-      <c r="D178" s="73" t="s">
-        <v>155</v>
+      <c r="I177" s="72"/>
+      <c r="J177" s="72"/>
+      <c r="K177" s="72"/>
+    </row>
+    <row r="178" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B178" s="31"/>
+      <c r="C178" s="38"/>
+      <c r="D178" s="82" t="s">
+        <v>175</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
-      <c r="H178" s="58">
+      <c r="H178" s="57">
         <v>0</v>
       </c>
-      <c r="I178" s="66"/>
-      <c r="J178" s="66"/>
-      <c r="K178" s="66"/>
-    </row>
-    <row r="179" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B179" s="32"/>
-      <c r="C179" s="39"/>
-      <c r="D179" s="32" t="s">
-        <v>156</v>
+      <c r="I178" s="72"/>
+      <c r="J178" s="72"/>
+      <c r="K178" s="72"/>
+    </row>
+    <row r="179" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B179" s="31"/>
+      <c r="C179" s="38"/>
+      <c r="D179" s="31" t="s">
+        <v>176</v>
       </c>
       <c r="E179" s="2"/>
-      <c r="F179" s="35"/>
-      <c r="G179" s="58"/>
-      <c r="H179" s="58">
+      <c r="F179" s="34"/>
+      <c r="G179" s="57"/>
+      <c r="H179" s="57">
         <v>0</v>
       </c>
-      <c r="I179" s="66"/>
-      <c r="J179" s="66"/>
-      <c r="K179" s="66"/>
-    </row>
-    <row r="180" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B180" s="32"/>
-      <c r="C180" s="39"/>
-      <c r="D180" s="32" t="s">
-        <v>157</v>
+      <c r="I179" s="72"/>
+      <c r="J179" s="72"/>
+      <c r="K179" s="72"/>
+    </row>
+    <row r="180" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B180" s="31"/>
+      <c r="C180" s="38"/>
+      <c r="D180" s="31" t="s">
+        <v>177</v>
       </c>
       <c r="E180" s="2"/>
-      <c r="F180" s="35"/>
-      <c r="G180" s="58"/>
-      <c r="H180" s="58">
+      <c r="F180" s="34"/>
+      <c r="G180" s="57"/>
+      <c r="H180" s="57">
         <v>0</v>
       </c>
-      <c r="I180" s="66"/>
-      <c r="J180" s="66"/>
-      <c r="K180" s="66"/>
-    </row>
-    <row r="181" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B181" s="32"/>
-      <c r="C181" s="39"/>
-      <c r="D181" s="32" t="s">
-        <v>158</v>
+      <c r="I180" s="72"/>
+      <c r="J180" s="72"/>
+      <c r="K180" s="72"/>
+    </row>
+    <row r="181" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B181" s="31"/>
+      <c r="C181" s="38"/>
+      <c r="D181" s="31" t="s">
+        <v>178</v>
       </c>
       <c r="E181" s="2"/>
-      <c r="F181" s="35"/>
-      <c r="G181" s="58"/>
-      <c r="H181" s="58">
+      <c r="F181" s="34"/>
+      <c r="G181" s="57"/>
+      <c r="H181" s="57">
         <v>200</v>
       </c>
-      <c r="I181" s="66"/>
-      <c r="J181" s="95"/>
-      <c r="K181" s="66"/>
-    </row>
-    <row r="182" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B182" s="32"/>
-      <c r="C182" s="39"/>
-      <c r="D182" s="32" t="s">
-        <v>159</v>
+      <c r="I181" s="72"/>
+      <c r="J181" s="107"/>
+      <c r="K181" s="72"/>
+    </row>
+    <row r="182" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B182" s="31"/>
+      <c r="C182" s="38"/>
+      <c r="D182" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="E182" s="2"/>
-      <c r="F182" s="35"/>
-      <c r="G182" s="58"/>
-      <c r="H182" s="56">
+      <c r="F182" s="34"/>
+      <c r="G182" s="57"/>
+      <c r="H182" s="55">
         <v>790</v>
       </c>
-      <c r="I182" s="66"/>
-      <c r="J182" s="66"/>
-      <c r="K182" s="66"/>
-    </row>
-    <row r="183" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B183" s="32"/>
-      <c r="C183" s="39"/>
-      <c r="D183" s="32" t="s">
-        <v>160</v>
+      <c r="I182" s="72"/>
+      <c r="J182" s="72"/>
+      <c r="K182" s="72"/>
+    </row>
+    <row r="183" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B183" s="31"/>
+      <c r="C183" s="38"/>
+      <c r="D183" s="31" t="s">
+        <v>180</v>
       </c>
       <c r="E183" s="2"/>
-      <c r="F183" s="35"/>
-      <c r="G183" s="58"/>
-      <c r="H183" s="58">
-        <v>750</v>
-      </c>
-      <c r="I183" s="66"/>
-      <c r="J183" s="66"/>
-      <c r="K183" s="66"/>
-    </row>
-    <row r="184" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B184" s="32"/>
-      <c r="C184" s="39"/>
-      <c r="D184" s="32" t="s">
-        <v>161</v>
+      <c r="F183" s="34"/>
+      <c r="G183" s="57"/>
+      <c r="H183" s="57">
+        <v>13480</v>
+      </c>
+      <c r="I183" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="J183" s="78"/>
+      <c r="K183" s="78"/>
+      <c r="L183" s="58"/>
+      <c r="M183" s="58"/>
+      <c r="N183" s="58"/>
+    </row>
+    <row r="184" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B184" s="31"/>
+      <c r="C184" s="38"/>
+      <c r="D184" s="31" t="s">
+        <v>182</v>
       </c>
       <c r="E184" s="2"/>
-      <c r="F184" s="35"/>
-      <c r="G184" s="58"/>
-      <c r="H184" s="58">
+      <c r="F184" s="34"/>
+      <c r="G184" s="57"/>
+      <c r="H184" s="57">
         <v>0</v>
       </c>
-      <c r="I184" s="66"/>
-      <c r="J184" s="66"/>
-      <c r="K184" s="66"/>
-    </row>
-    <row r="185" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B185" s="32"/>
-      <c r="C185" s="39"/>
-      <c r="D185" s="39" t="s">
-        <v>162</v>
+      <c r="I184" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="J184" s="95"/>
+      <c r="K184" s="95"/>
+      <c r="L184" s="60"/>
+      <c r="M184" s="108"/>
+      <c r="N184" s="108"/>
+      <c r="O184" s="108"/>
+    </row>
+    <row r="185" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B185" s="31"/>
+      <c r="C185" s="38"/>
+      <c r="D185" s="38" t="s">
+        <v>184</v>
       </c>
       <c r="E185" s="2"/>
-      <c r="F185" s="35"/>
-      <c r="G185" s="58"/>
-      <c r="H185" s="56">
-        <v>22938</v>
-      </c>
-      <c r="I185" s="66"/>
-      <c r="J185" s="66"/>
-      <c r="K185" s="66"/>
-    </row>
-    <row r="186" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B186" s="32"/>
-      <c r="C186" s="39"/>
-      <c r="D186" s="122" t="s">
-        <v>195</v>
+      <c r="F185" s="34"/>
+      <c r="G185" s="57"/>
+      <c r="H185" s="150">
+        <v>24895</v>
+      </c>
+      <c r="I185" s="72"/>
+      <c r="J185" s="72"/>
+      <c r="K185" s="72"/>
+    </row>
+    <row r="186" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B186" s="31"/>
+      <c r="C186" s="38"/>
+      <c r="D186" s="38" t="s">
+        <v>185</v>
       </c>
       <c r="E186" s="2"/>
-      <c r="F186" s="35"/>
+      <c r="F186" s="34"/>
       <c r="G186" s="2"/>
-      <c r="H186" s="56"/>
-      <c r="I186" s="66"/>
-      <c r="J186" s="66"/>
-      <c r="K186" s="66"/>
-    </row>
-    <row r="187" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B187" s="32"/>
-      <c r="C187" s="39"/>
-      <c r="D187" s="39" t="s">
-        <v>163</v>
+      <c r="H186" s="55"/>
+      <c r="I186" s="72"/>
+      <c r="J186" s="72"/>
+      <c r="K186" s="72"/>
+    </row>
+    <row r="187" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B187" s="31"/>
+      <c r="C187" s="38"/>
+      <c r="D187" s="38" t="s">
+        <v>186</v>
       </c>
       <c r="E187" s="2"/>
-      <c r="F187" s="35"/>
+      <c r="F187" s="34"/>
       <c r="G187" s="2"/>
-      <c r="H187" s="56">
+      <c r="H187" s="55">
         <v>675</v>
       </c>
-      <c r="I187" s="66"/>
-      <c r="J187" s="66"/>
-      <c r="K187" s="66"/>
-    </row>
-    <row r="188" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B188" s="132" t="s">
-        <v>164</v>
-      </c>
-      <c r="C188" s="133"/>
-      <c r="D188" s="134"/>
-      <c r="E188" s="96"/>
-      <c r="F188" s="97"/>
-      <c r="G188" s="96"/>
-      <c r="H188" s="98">
+      <c r="I187" s="72"/>
+      <c r="J187" s="72"/>
+      <c r="K187" s="72"/>
+    </row>
+    <row r="188" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B188" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="C188" s="134"/>
+      <c r="D188" s="135"/>
+      <c r="E188" s="109"/>
+      <c r="F188" s="110"/>
+      <c r="G188" s="109"/>
+      <c r="H188" s="111">
         <f>H20+H36+H39+H48+H55+H66+H74+H82+H98+H110+H125+H133+H137+H142+H149+H159+H168</f>
-        <v>909561</v>
-      </c>
-    </row>
-    <row r="189" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B189" s="32"/>
-      <c r="C189" s="39"/>
-      <c r="D189" s="32"/>
+        <v>947168</v>
+      </c>
+    </row>
+    <row r="189" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B189" s="31"/>
+      <c r="C189" s="38"/>
+      <c r="D189" s="31"/>
       <c r="E189" s="2"/>
-      <c r="F189" s="35"/>
+      <c r="F189" s="34"/>
       <c r="G189" s="2"/>
-      <c r="H189" s="58"/>
-    </row>
-    <row r="190" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B190" s="32"/>
-      <c r="C190" s="39"/>
-      <c r="D190" s="32"/>
+      <c r="H189" s="57"/>
+    </row>
+    <row r="190" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B190" s="31"/>
+      <c r="C190" s="38"/>
+      <c r="D190" s="31"/>
       <c r="E190" s="2"/>
-      <c r="F190" s="35"/>
+      <c r="F190" s="34"/>
       <c r="G190" s="2"/>
-      <c r="H190" s="58"/>
-    </row>
-    <row r="191" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B191" s="127" t="s">
-        <v>165</v>
-      </c>
-      <c r="C191" s="128"/>
-      <c r="D191" s="129"/>
-      <c r="E191" s="127"/>
-      <c r="F191" s="128"/>
-      <c r="G191" s="129"/>
-      <c r="H191" s="99">
+      <c r="H190" s="57"/>
+    </row>
+    <row r="191" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B191" s="128" t="s">
+        <v>188</v>
+      </c>
+      <c r="C191" s="129"/>
+      <c r="D191" s="130"/>
+      <c r="E191" s="128"/>
+      <c r="F191" s="129"/>
+      <c r="G191" s="130"/>
+      <c r="H191" s="112">
         <f>SUM(H194:H203)</f>
-        <v>312190.93</v>
-      </c>
-    </row>
-    <row r="192" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B192" s="32"/>
-      <c r="C192" s="39"/>
-      <c r="D192" s="32"/>
+        <v>317079.84000000003</v>
+      </c>
+    </row>
+    <row r="192" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B192" s="31"/>
+      <c r="C192" s="38"/>
+      <c r="D192" s="31"/>
       <c r="E192" s="2"/>
-      <c r="F192" s="35"/>
-      <c r="H192" s="100"/>
-      <c r="I192" s="101"/>
+      <c r="F192" s="34"/>
+      <c r="H192" s="113"/>
+      <c r="I192" s="114"/>
     </row>
     <row r="193" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B193" s="53" t="s">
-        <v>166</v>
-      </c>
-      <c r="C193" s="39"/>
-      <c r="D193" s="33" t="s">
-        <v>167</v>
+      <c r="B193" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="C193" s="38"/>
+      <c r="D193" s="32" t="s">
+        <v>190</v>
       </c>
       <c r="E193" s="2"/>
-      <c r="F193" s="35"/>
+      <c r="F193" s="34"/>
       <c r="G193" s="2"/>
-      <c r="H193" s="102"/>
-      <c r="I193" s="101"/>
+      <c r="H193" s="115"/>
+      <c r="I193" s="114"/>
     </row>
     <row r="194" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B194" s="32"/>
-      <c r="C194" s="39"/>
-      <c r="D194" s="32" t="s">
-        <v>168</v>
+      <c r="B194" s="31"/>
+      <c r="C194" s="38"/>
+      <c r="D194" s="31" t="s">
+        <v>191</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
-      <c r="H194" s="102">
+      <c r="H194" s="115">
         <f>E194*G194</f>
         <v>0</v>
       </c>
-      <c r="I194" s="101"/>
+      <c r="I194" s="114"/>
     </row>
     <row r="195" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B195" s="32"/>
-      <c r="C195" s="39"/>
-      <c r="D195" s="32" t="s">
-        <v>169</v>
+      <c r="B195" s="31"/>
+      <c r="C195" s="38"/>
+      <c r="D195" s="31" t="s">
+        <v>192</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="F195" s="2">
         <v>15</v>
       </c>
-      <c r="G195" s="103">
+      <c r="G195" s="116">
         <v>3200</v>
       </c>
-      <c r="H195" s="102">
+      <c r="H195" s="115">
         <f t="shared" ref="H195:H196" si="10">SUM(F195*G195)</f>
         <v>48000</v>
       </c>
-      <c r="I195" s="101"/>
+      <c r="I195" s="114"/>
     </row>
     <row r="196" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B196" s="32"/>
-      <c r="C196" s="39"/>
-      <c r="D196" s="32" t="s">
-        <v>171</v>
+      <c r="B196" s="31"/>
+      <c r="C196" s="38"/>
+      <c r="D196" s="31" t="s">
+        <v>194</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="F196" s="2">
         <v>25</v>
       </c>
-      <c r="G196" s="103">
+      <c r="G196" s="116">
         <v>3950</v>
       </c>
-      <c r="H196" s="102">
+      <c r="H196" s="115">
         <f t="shared" si="10"/>
         <v>98750</v>
       </c>
-      <c r="I196" s="101"/>
+      <c r="I196" s="114"/>
     </row>
     <row r="197" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B197" s="32"/>
-      <c r="C197" s="39"/>
-      <c r="D197" s="32" t="s">
-        <v>172</v>
+      <c r="B197" s="31"/>
+      <c r="C197" s="38"/>
+      <c r="D197" s="31" t="s">
+        <v>195</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G197" s="103" t="s">
-        <v>174</v>
-      </c>
-      <c r="H197" s="102">
+        <v>196</v>
+      </c>
+      <c r="G197" s="116" t="s">
+        <v>197</v>
+      </c>
+      <c r="H197" s="115">
         <v>24000</v>
       </c>
-      <c r="I197" s="101"/>
+      <c r="I197" s="114"/>
     </row>
     <row r="198" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B198" s="32"/>
-      <c r="C198" s="39"/>
-      <c r="D198" s="32" t="s">
-        <v>175</v>
+      <c r="B198" s="31"/>
+      <c r="C198" s="38"/>
+      <c r="D198" s="31" t="s">
+        <v>198</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G198" s="103">
+        <v>199</v>
+      </c>
+      <c r="G198" s="116">
         <v>1350</v>
       </c>
-      <c r="H198" s="102">
+      <c r="H198" s="115">
         <v>9450</v>
       </c>
-      <c r="I198" s="101"/>
+      <c r="I198" s="114"/>
     </row>
     <row r="199" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B199" s="32"/>
-      <c r="C199" s="39"/>
-      <c r="D199" s="32" t="s">
-        <v>177</v>
+      <c r="B199" s="31"/>
+      <c r="C199" s="38"/>
+      <c r="D199" s="31" t="s">
+        <v>200</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
-      <c r="H199" s="104">
+      <c r="H199" s="117">
         <v>13748</v>
       </c>
-      <c r="I199" s="101"/>
+      <c r="I199" s="114"/>
     </row>
     <row r="200" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B200" s="32"/>
-      <c r="C200" s="39"/>
-      <c r="D200" s="39" t="s">
-        <v>63</v>
+      <c r="B200" s="31"/>
+      <c r="C200" s="38"/>
+      <c r="D200" s="38" t="s">
+        <v>74</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
-      <c r="H200" s="102">
+      <c r="H200" s="115">
         <f>E200*G200</f>
         <v>0</v>
       </c>
-      <c r="I200" s="101"/>
+      <c r="I200" s="114"/>
     </row>
     <row r="201" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B201" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="C201" s="39"/>
-      <c r="D201" s="32"/>
+      <c r="B201" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="C201" s="38"/>
+      <c r="D201" s="31"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
-      <c r="H201" s="102"/>
-      <c r="I201" s="101"/>
-      <c r="K201" s="125"/>
+      <c r="H201" s="115"/>
+      <c r="I201" s="114"/>
+      <c r="K201" s="69"/>
     </row>
     <row r="202" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B202" s="139" t="s">
-        <v>179</v>
-      </c>
-      <c r="C202" s="140"/>
-      <c r="D202" s="140"/>
-      <c r="E202" s="105" t="s">
-        <v>180</v>
-      </c>
-      <c r="F202" s="106">
+      <c r="B202" s="140" t="s">
+        <v>202</v>
+      </c>
+      <c r="C202" s="141"/>
+      <c r="D202" s="141"/>
+      <c r="E202" s="118" t="s">
+        <v>203</v>
+      </c>
+      <c r="F202" s="119">
         <v>0.115</v>
       </c>
-      <c r="G202" s="107">
+      <c r="G202" s="120">
         <f>SUM(H188*F202)</f>
-        <v>104599.515</v>
-      </c>
-      <c r="H202" s="104">
+        <v>108924.32</v>
+      </c>
+      <c r="H202" s="117">
         <f>G202</f>
-        <v>104599.515</v>
-      </c>
-      <c r="I202" s="101"/>
+        <v>108924.32</v>
+      </c>
+      <c r="I202" s="114"/>
     </row>
     <row r="203" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B203" s="130" t="s">
-        <v>181</v>
-      </c>
-      <c r="C203" s="131"/>
-      <c r="D203" s="131"/>
+      <c r="B203" s="131" t="s">
+        <v>204</v>
+      </c>
+      <c r="C203" s="132"/>
+      <c r="D203" s="132"/>
       <c r="E203" s="2"/>
-      <c r="F203" s="105">
+      <c r="F203" s="118">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G203" s="107"/>
-      <c r="H203" s="108">
+      <c r="G203" s="120"/>
+      <c r="H203" s="121">
         <f>SUM(F203*H188)</f>
-        <v>13643.414999999999</v>
-      </c>
-      <c r="I203" s="101"/>
+        <v>14207.519999999999</v>
+      </c>
+      <c r="I203" s="114"/>
     </row>
     <row r="204" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B204" s="132" t="s">
-        <v>182</v>
-      </c>
-      <c r="C204" s="133"/>
-      <c r="D204" s="134"/>
-      <c r="E204" s="96"/>
-      <c r="F204" s="97"/>
-      <c r="G204" s="96"/>
-      <c r="H204" s="109">
+      <c r="B204" s="133" t="s">
+        <v>205</v>
+      </c>
+      <c r="C204" s="134"/>
+      <c r="D204" s="135"/>
+      <c r="E204" s="109"/>
+      <c r="F204" s="110"/>
+      <c r="G204" s="109"/>
+      <c r="H204" s="122">
         <f>SUM(H188+H191)</f>
-        <v>1221751.93</v>
-      </c>
-      <c r="I204" s="121" t="s">
-        <v>198</v>
-      </c>
-      <c r="J204" s="121"/>
-      <c r="K204" s="121"/>
-      <c r="L204" s="121"/>
-      <c r="M204" s="121"/>
-      <c r="N204" s="121"/>
-      <c r="O204" s="121"/>
-      <c r="P204" s="121"/>
-      <c r="Q204" s="121"/>
-      <c r="R204" s="121"/>
-      <c r="S204" s="121"/>
-      <c r="T204" s="121"/>
-      <c r="U204" s="121"/>
-      <c r="V204" s="121"/>
-      <c r="W204" s="121"/>
+        <v>1264247.8400000001</v>
+      </c>
+      <c r="I204" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="J204" s="58"/>
+      <c r="K204" s="58"/>
+      <c r="L204" s="58"/>
+      <c r="M204" s="58"/>
+      <c r="N204" s="58"/>
+      <c r="O204" s="58"/>
+      <c r="P204" s="58"/>
+      <c r="Q204" s="58"/>
+      <c r="R204" s="58"/>
+      <c r="S204" s="58"/>
+      <c r="T204" s="58"/>
+      <c r="U204" s="58"/>
+      <c r="V204" s="58"/>
+      <c r="W204" s="58"/>
     </row>
     <row r="205" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B205" s="32"/>
-      <c r="C205" s="39"/>
-      <c r="D205" s="32"/>
+      <c r="B205" s="31"/>
+      <c r="C205" s="38"/>
+      <c r="D205" s="31"/>
       <c r="E205" s="2"/>
-      <c r="F205" s="35"/>
+      <c r="F205" s="34"/>
       <c r="G205" s="2"/>
-      <c r="H205" s="58"/>
-      <c r="I205" s="101"/>
+      <c r="H205" s="57"/>
+      <c r="I205" s="114"/>
     </row>
     <row r="206" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B206" s="135" t="s">
-        <v>183</v>
-      </c>
-      <c r="C206" s="136"/>
-      <c r="D206" s="137"/>
-      <c r="E206" s="110"/>
-      <c r="F206" s="110"/>
-      <c r="G206" s="110"/>
-      <c r="H206" s="110"/>
+      <c r="B206" s="136" t="s">
+        <v>207</v>
+      </c>
+      <c r="C206" s="137"/>
+      <c r="D206" s="138"/>
+      <c r="E206" s="123"/>
+      <c r="F206" s="123"/>
+      <c r="G206" s="123"/>
+      <c r="H206" s="123"/>
     </row>
     <row r="207" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B207" s="32"/>
-      <c r="C207" s="39"/>
-      <c r="D207" s="32"/>
+      <c r="B207" s="31"/>
+      <c r="C207" s="38"/>
+      <c r="D207" s="31"/>
       <c r="E207" s="2"/>
-      <c r="F207" s="35"/>
+      <c r="F207" s="34"/>
       <c r="G207" s="2"/>
-      <c r="H207" s="58"/>
+      <c r="H207" s="57"/>
     </row>
     <row r="208" spans="2:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B208" s="32"/>
-      <c r="C208" s="39"/>
-      <c r="D208" s="32" t="s">
-        <v>184</v>
+      <c r="B208" s="31"/>
+      <c r="C208" s="38"/>
+      <c r="D208" s="31" t="s">
+        <v>208</v>
       </c>
       <c r="E208" s="2"/>
-      <c r="F208" s="111">
+      <c r="F208" s="124">
         <v>0.115</v>
       </c>
       <c r="G208" s="2"/>
-      <c r="H208" s="112">
+      <c r="H208" s="125">
         <v>0.115</v>
       </c>
     </row>
-    <row r="209" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B209" s="32"/>
-      <c r="C209" s="39"/>
-      <c r="D209" s="32" t="s">
-        <v>185</v>
+    <row r="209" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B209" s="31"/>
+      <c r="C209" s="38"/>
+      <c r="D209" s="31" t="s">
+        <v>209</v>
       </c>
       <c r="E209" s="2"/>
-      <c r="F209" s="113">
+      <c r="F209" s="126">
         <v>9200</v>
       </c>
       <c r="G209" s="2"/>
-      <c r="H209" s="58">
+      <c r="H209" s="57">
         <v>9200</v>
       </c>
     </row>
-    <row r="210" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B210" s="32"/>
-      <c r="C210" s="39"/>
-      <c r="D210" s="32" t="s">
-        <v>186</v>
+    <row r="210" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B210" s="31"/>
+      <c r="C210" s="38"/>
+      <c r="D210" s="31" t="s">
+        <v>210</v>
       </c>
       <c r="E210" s="2"/>
-      <c r="F210" s="114" t="s">
-        <v>187</v>
+      <c r="F210" s="127" t="s">
+        <v>211</v>
       </c>
       <c r="G210" s="2"/>
-      <c r="H210" s="58">
+      <c r="H210" s="57">
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B211" s="32"/>
-      <c r="C211" s="39"/>
-      <c r="D211" s="123" t="s">
-        <v>194</v>
+    <row r="211" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B211" s="31"/>
+      <c r="C211" s="38"/>
+      <c r="D211" s="31" t="s">
+        <v>212</v>
       </c>
       <c r="E211" s="2"/>
-      <c r="F211" s="35"/>
+      <c r="F211" s="34"/>
       <c r="G211" s="2"/>
-      <c r="H211" s="58">
-        <v>13480</v>
-      </c>
-    </row>
-    <row r="212" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B212" s="32"/>
-      <c r="C212" s="39"/>
-      <c r="D212" s="123" t="s">
-        <v>193</v>
-      </c>
+      <c r="H211" s="57">
+        <v>27275</v>
+      </c>
+    </row>
+    <row r="212" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B212" s="31"/>
+      <c r="C212" s="38"/>
+      <c r="D212" s="31"/>
       <c r="E212" s="2"/>
-      <c r="F212" s="35"/>
+      <c r="F212" s="34"/>
       <c r="G212" s="2"/>
-      <c r="H212" s="58">
-        <v>27275</v>
-      </c>
-    </row>
-    <row r="213" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B213" s="32"/>
-      <c r="C213" s="39"/>
-      <c r="D213" s="32" t="s">
-        <v>205</v>
-      </c>
-      <c r="E213" s="2"/>
-      <c r="F213" s="35"/>
+      <c r="H212" s="31"/>
+    </row>
+    <row r="213" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B213" s="31"/>
+      <c r="C213" s="38"/>
+      <c r="D213" s="31"/>
+      <c r="E213" s="31"/>
+      <c r="F213" s="34"/>
       <c r="G213" s="2"/>
-      <c r="H213" s="126">
-        <v>69905</v>
-      </c>
-      <c r="I213" s="121" t="s">
-        <v>209</v>
-      </c>
-      <c r="J213" s="121"/>
-      <c r="K213" s="121"/>
-      <c r="L213" s="121"/>
-    </row>
-    <row r="214" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B214" s="32"/>
-      <c r="C214" s="39"/>
-      <c r="D214" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="E214" s="2"/>
-      <c r="F214" s="35"/>
+      <c r="H213" s="31"/>
+    </row>
+    <row r="214" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C214" s="1"/>
+      <c r="F214" s="2"/>
       <c r="G214" s="2"/>
-      <c r="H214" s="126">
-        <v>80000</v>
-      </c>
-      <c r="I214" s="121" t="s">
-        <v>210</v>
-      </c>
-      <c r="J214" s="121"/>
-      <c r="K214" s="121"/>
-      <c r="L214" s="121"/>
-      <c r="M214" s="121"/>
-      <c r="N214" s="121"/>
-      <c r="O214" s="121"/>
-      <c r="P214" s="121"/>
-      <c r="Q214" s="121"/>
-      <c r="R214" s="121"/>
-    </row>
-    <row r="215" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B215" s="32"/>
-      <c r="C215" s="39"/>
-      <c r="D215" s="32"/>
-      <c r="E215" s="2"/>
-      <c r="F215" s="35"/>
+    </row>
+    <row r="215" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C215" s="1"/>
+      <c r="F215" s="2"/>
       <c r="G215" s="2"/>
-      <c r="H215" s="32"/>
-    </row>
-    <row r="216" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B216" s="32"/>
-      <c r="C216" s="39"/>
-      <c r="D216" s="32"/>
-      <c r="E216" s="32"/>
-      <c r="F216" s="35"/>
+    </row>
+    <row r="216" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C216" s="1"/>
+      <c r="F216" s="2"/>
       <c r="G216" s="2"/>
-      <c r="H216" s="32"/>
-    </row>
-    <row r="217" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="217" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C217" s="1"/>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
     </row>
-    <row r="218" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C218" s="1"/>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
     </row>
-    <row r="219" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C219" s="1"/>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
     </row>
-    <row r="220" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C220" s="1"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
     </row>
-    <row r="221" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C221" s="1"/>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
     </row>
-    <row r="222" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C222" s="1"/>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
     </row>
-    <row r="223" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C223" s="1"/>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
     </row>
-    <row r="224" spans="2:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C224" s="1"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
@@ -9777,21 +9829,6 @@
       <c r="C997" s="1"/>
       <c r="F997" s="2"/>
       <c r="G997" s="2"/>
-    </row>
-    <row r="998" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C998" s="1"/>
-      <c r="F998" s="2"/>
-      <c r="G998" s="2"/>
-    </row>
-    <row r="999" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C999" s="1"/>
-      <c r="F999" s="2"/>
-      <c r="G999" s="2"/>
-    </row>
-    <row r="1000" spans="3:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C1000" s="1"/>
-      <c r="F1000" s="2"/>
-      <c r="G1000" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -9822,7 +9859,7 @@
     <mergeCell ref="B191:D191"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>